--- a/LakeMeadWaterBankDivideInflow.xlsx
+++ b/LakeMeadWaterBankDivideInflow.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anabelle/Documents/LakeMeadDivideInflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2133D94C-ACC9-0847-9CA7-B7D82E75B677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E388BF-DB80-2343-A335-83E2005A8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17120" yWindow="-24000" windowWidth="38400" windowHeight="24000" activeTab="3" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
+    <workbookView xWindow="-17120" yWindow="-24000" windowWidth="38400" windowHeight="24000" activeTab="2" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe-Directions" sheetId="62" r:id="rId1"/>
@@ -26,83 +26,9 @@
     <sheet name="Mead-Elevation-Area" sheetId="10" r:id="rId11"/>
     <sheet name="CellType" sheetId="54" r:id="rId12"/>
     <sheet name="BasinConservationPrograms" sheetId="65" r:id="rId13"/>
-    <sheet name="LakeMeadInflowScenarios" sheetId="64" r:id="rId14"/>
-    <sheet name="DynamicPlotData" sheetId="68" r:id="rId15"/>
+    <sheet name="DynamicPlotData" sheetId="68" r:id="rId14"/>
+    <sheet name="LakeMeadInflowScenarios" sheetId="64" r:id="rId15"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.57" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.58" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">Master!$C$142:$G$142</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">Master!$C$143:$G$143</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">Master!$C$144:$G$144</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">Master!$C$145:$G$145</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">Master!$C$146:$G$146</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">Master!$C$147:$G$147</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">Master!$C$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">DynamicPlotData!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Master!$C$142:$G$142</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -123,8 +49,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="488">
   <si>
     <t>Year 1</t>
   </si>
@@ -2406,16 +2354,26 @@
     <t>Protection Elevation [ft] without withdrawals</t>
   </si>
   <si>
-    <t>Chosen Protection Elevation</t>
-  </si>
-  <si>
     <t>DCP Trigger</t>
   </si>
   <si>
-    <t>Min Power Pool</t>
+    <t>Min Power Pool: 955 ft</t>
   </si>
   <si>
-    <t>Final EIS Buffer Line</t>
+    <t>Final EIS Buffer Line: 975 ft</t>
+  </si>
+  <si>
+    <t>Tribal Nations</t>
+  </si>
+  <si>
+    <t>End of Year Balance</t>
+  </si>
+  <si>
+    <t>Reclamation Protect
+Zone</t>
+  </si>
+  <si>
+    <t>End of Year Balance Data Labels</t>
   </si>
 </sst>
 </file>
@@ -3374,7 +3332,7 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="457">
+  <cellXfs count="461">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4306,6 +4264,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4624,6 +4583,13 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="20% - Accent1" xfId="12" builtinId="30"/>
@@ -4641,7 +4607,157 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="95">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -5042,20 +5158,420 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF007EF2"/>
+      <color rgb="FF0068C8"/>
+      <color rgb="FF0073DC"/>
+      <color rgb="FF007DEF"/>
       <color rgb="FF529BE7"/>
       <color rgb="FF3C82C0"/>
       <color rgb="FF528CBF"/>
       <color rgb="FF7AB5F2"/>
       <color rgb="FF5CA7F1"/>
-      <color rgb="FF007DEF"/>
       <color rgb="FF0077DB"/>
-      <color rgb="FF0086EC"/>
-      <color rgb="FF007AD6"/>
-      <color rgb="FF528EDC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5090,8 +5606,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.0901785917221303E-2"/>
-          <c:y val="3.4536042119895576E-2"/>
+          <c:x val="8.2365242264845109E-2"/>
+          <c:y val="3.4537023781118267E-2"/>
           <c:w val="0.91173420288821727"/>
           <c:h val="0.90589663262331543"/>
         </c:manualLayout>
@@ -5119,418 +5635,177 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Master!$C$27:$G$27</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Year 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Year 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Year 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Year 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Year 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Master!$C$142:$G$142</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C502-0346-B214-A35A0297EDD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Tribal Nations</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Master!$C$147:$G$147</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C502-0346-B214-A35A0297EDD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Mexico</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="3C82C0"/>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Master!$C$146:$G$146</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C502-0346-B214-A35A0297EDD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>Nevada</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="529BE7"/>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Master!$C$27:$G$27</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Year 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Year 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Year 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Year 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Year 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Master!$C$145:$G$145</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C502-0346-B214-A35A0297EDD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>Arizona</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="7AB5F2"/>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6D24E5FC-1654-6947-839F-964DB2CA094A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{72934C22-0618-9F4B-8AE7-B79C7868C9B0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C21D1A2C-6282-9743-A7F1-5F1B558BE6B0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001C-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{14A3BFD1-22BA-674D-AF1C-FADC2ABD3D23}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F0E1BBA5-915F-C048-A98C-C9A536F16FDB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="0.0;;;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -5559,14 +5834,15 @@
             </c:txPr>
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -5596,7 +5872,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Master!$C$144:$G$144</c:f>
+              <c:f>Master!$C$142:$G$142</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
@@ -5619,23 +5895,28 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$23:$F$23</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C502-0346-B214-A35A0297EDD2}"/>
+              <c16:uniqueId val="{00000000-C502-0346-B214-A35A0297EDD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="5"/>
+          <c:idx val="5"/>
+          <c:order val="1"/>
           <c:tx>
-            <c:v>California</c:v>
+            <c:v>Tribal Nations</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
-              </a:schemeClr>
+              <a:srgbClr val="0068C8"/>
             </a:solidFill>
             <a:ln w="12700">
               <a:solidFill>
@@ -5646,6 +5927,177 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{525EF4FE-6C61-214E-A54E-4D55904B160B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002E-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2A4B2256-B98F-ED41-9D96-6150B3EBD74B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002F-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{3274F16B-47DA-8A47-B58B-1F92A236A5FE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000030-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{45DF277B-9831-AB4A-AFFA-A8EC895531FD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000031-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{7C67022F-7788-AE40-8DB3-B6AC4217E0DB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000032-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.0;\-#,##0.0;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -5674,14 +6126,553 @@
             </c:txPr>
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Master!$C$147:$G$147</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$22:$F$22</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C502-0346-B214-A35A0297EDD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Mexico</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007EF2"/>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{158A015D-D354-2E4D-A4EB-502E0C84880B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000024-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C02BD27C-BC4F-C34E-88D4-40F3FDFBA8EA}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000025-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6F26EA52-4B94-3E4F-B0FC-8E5CA7786468}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000026-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DA0DDC15-479E-1947-BCDB-E77E7C2D5781}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000027-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{EBEB41C6-0067-7740-97BF-32048C9DC0C4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000028-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.0;\-#,##0.0;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Master!$C$146:$G$146</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$21:$F$21</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C502-0346-B214-A35A0297EDD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Nevada</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="529BE7"/>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DAA6EC7F-54E3-8043-9D21-3B2E3F400D74}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000029-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{744498B0-F271-FF46-97AE-1FDB7D557FF1}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002A-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{8A509EC7-2C02-2740-A8B3-0482D2A58E7D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002B-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6A15D912-EC3E-0748-9FA3-091A7949E1BB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002C-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2C6CB93D-783C-8240-9677-AE783C99D599}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002D-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.0;\-#,##0.0;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -5711,6 +6702,593 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>Master!$C$145:$G$145</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$20:$F$20</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C502-0346-B214-A35A0297EDD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Arizona</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7AB5F2"/>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{89EC99EE-31B2-2648-B269-B2F9E13BE846}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001F-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{070111C5-EDF9-D34F-9552-8CD0A7A9C22F}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000020-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{27744255-E334-294B-A8E2-DB08D4FA7D47}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000021-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B2E64831-4952-2F46-9D05-19383E57DDAC}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000022-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{8B381459-5668-5D4E-AB04-793C69287278}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000023-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.0;\-#,##0.0;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Master!$C$27:$G$27</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Year 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Year 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Year 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Year 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Master!$C$144:$G$144</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$19:$F$19</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C502-0346-B214-A35A0297EDD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>California</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AA4C0E14-7AF3-144F-B0CB-01238F726396}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D64EC274-DCCC-8F41-B30E-FFC30047DC83}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{32DAA80A-6151-424C-A4AB-911C496E573E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5E9ECFCB-58F2-B743-9A2F-FDED1119B5FC}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6EB25BD2-3AF1-644B-8735-E39BD97FD70D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="0.0;;;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Master!$C$27:$G$27</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Year 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Year 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Year 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Year 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>Master!$C$143:$G$143</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
@@ -5734,14 +7312,23 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>DynamicPlotData!$B$18:$F$18</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C502-0346-B214-A35A0297EDD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -5752,6 +7339,669 @@
         <c:axId val="1147498848"/>
         <c:axId val="1147518256"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DynamicPlotData!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Chosen Protect Elevation:  ft</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="3175" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-733D-FF48-8586-837D5AB1AA55}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-733D-FF48-8586-837D5AB1AA55}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-733D-FF48-8586-837D5AB1AA55}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.7804881421351313E-3"/>
+                  <c:y val="-2.2222142686709617E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{74915F78-F47B-DC47-A4A0-B9EC69026CAB}" type="SERIESNAME">
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="bg2">
+                            <a:lumMod val="10000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr/>
+                      <a:t>[SERIES NAME]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.25966473054214445"/>
+                      <c:h val="6.5221151870952385E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-733D-FF48-8586-837D5AB1AA55}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-733D-FF48-8586-837D5AB1AA55}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="9144" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="0">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0.5"/>
+            <c:backward val="0.5"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>DynamicPlotData!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-733D-FF48-8586-837D5AB1AA55}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DynamicPlotData!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Min Power Pool: 955 ft</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="6350" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.3902440710675656E-3"/>
+                  <c:y val="-2.4242424242424315E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{106D0886-E17A-0E44-A014-ECA7EBA574E2}" type="SERIESNAME">
+                      <a:rPr lang="en-US" sz="1200" b="0"/>
+                      <a:pPr/>
+                      <a:t>[SERIES NAME]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="22225" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0.5"/>
+            <c:backward val="0.5"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>DynamicPlotData!$B$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.2231700000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2231700000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2231700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2231700000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2231700000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-21E7-644C-8ADD-F3F93D081EF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DynamicPlotData!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Final EIS Buffer Line: 975 ft</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="5.8536587614234211E-3"/>
+                  <c:y val="-2.8282828282828285E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{14EBAB83-0B43-5342-BFED-DE0AC9772BF5}" type="SERIESNAME">
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:pPr/>
+                      <a:t>[SERIES NAME]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-21E7-644C-8ADD-F3F93D081EF1}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0.5"/>
+            <c:backward val="0.5"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>DynamicPlotData!$B$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.1563530000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.1563530000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1563530000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.1563530000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.1563530000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-21E7-644C-8ADD-F3F93D081EF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1147498848"/>
+        <c:axId val="1147518256"/>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="1147498848"/>
         <c:scaling>
@@ -5895,13 +8145,19 @@
           </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="15875">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="35000"/>
+                <a:lumOff val="65000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -5923,8 +8179,10 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1147498848"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="1"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -16758,7 +19016,7 @@
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{CD5CBD06-5EA0-D143-9BD1-904F07A1EEEC}">
-  <sheetPr/>
+  <sheetPr codeName="Chart4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -16766,7 +19024,7 @@
 
 <file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{1C420103-4ACD-4AF8-BDB5-B91C302E6B07}">
-  <sheetPr/>
+  <sheetPr codeName="Chart8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -16977,7 +19235,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8667750" cy="6286500"/>
+    <xdr:ext cx="8678333" cy="6286500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -17575,6 +19833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2EA02F4-5F19-409C-8BC6-A0D8FEB3A90D}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -17593,20 +19852,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="377" t="s">
+      <c r="A1" s="378" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="377"/>
-      <c r="C1" s="377"/>
-      <c r="D1" s="377"/>
-      <c r="E1" s="377"/>
-      <c r="F1" s="377"/>
-      <c r="G1" s="377"/>
-      <c r="H1" s="377"/>
-      <c r="I1" s="377"/>
-      <c r="J1" s="377"/>
-      <c r="K1" s="377"/>
-      <c r="L1" s="377"/>
+      <c r="B1" s="378"/>
+      <c r="C1" s="378"/>
+      <c r="D1" s="378"/>
+      <c r="E1" s="378"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="378"/>
+      <c r="I1" s="378"/>
+      <c r="J1" s="378"/>
+      <c r="K1" s="378"/>
+      <c r="L1" s="378"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -17632,41 +19891,41 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:18" s="52" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="378" t="s">
+      <c r="A4" s="379" t="s">
         <v>296</v>
       </c>
-      <c r="B4" s="379"/>
-      <c r="C4" s="379"/>
-      <c r="D4" s="379"/>
-      <c r="E4" s="379"/>
-      <c r="F4" s="379"/>
-      <c r="G4" s="379"/>
-      <c r="H4" s="379"/>
-      <c r="I4" s="379"/>
-      <c r="J4" s="379"/>
-      <c r="K4" s="379"/>
-      <c r="L4" s="380"/>
-      <c r="N4" s="381"/>
-      <c r="O4" s="381"/>
-      <c r="P4" s="381"/>
-      <c r="Q4" s="381"/>
-      <c r="R4" s="381"/>
+      <c r="B4" s="380"/>
+      <c r="C4" s="380"/>
+      <c r="D4" s="380"/>
+      <c r="E4" s="380"/>
+      <c r="F4" s="380"/>
+      <c r="G4" s="380"/>
+      <c r="H4" s="380"/>
+      <c r="I4" s="380"/>
+      <c r="J4" s="380"/>
+      <c r="K4" s="380"/>
+      <c r="L4" s="381"/>
+      <c r="N4" s="382"/>
+      <c r="O4" s="382"/>
+      <c r="P4" s="382"/>
+      <c r="Q4" s="382"/>
+      <c r="R4" s="382"/>
     </row>
     <row r="5" spans="1:18" s="52" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="382" t="s">
+      <c r="A5" s="383" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="383"/>
-      <c r="C5" s="383"/>
-      <c r="D5" s="383"/>
-      <c r="E5" s="383"/>
-      <c r="F5" s="383"/>
-      <c r="G5" s="383"/>
-      <c r="H5" s="383"/>
-      <c r="I5" s="383"/>
-      <c r="J5" s="383"/>
-      <c r="K5" s="383"/>
-      <c r="L5" s="384"/>
+      <c r="B5" s="384"/>
+      <c r="C5" s="384"/>
+      <c r="D5" s="384"/>
+      <c r="E5" s="384"/>
+      <c r="F5" s="384"/>
+      <c r="G5" s="384"/>
+      <c r="H5" s="384"/>
+      <c r="I5" s="384"/>
+      <c r="J5" s="384"/>
+      <c r="K5" s="384"/>
+      <c r="L5" s="385"/>
       <c r="N5" s="110"/>
       <c r="O5" s="110"/>
       <c r="P5" s="110"/>
@@ -17674,20 +19933,20 @@
       <c r="R5" s="110"/>
     </row>
     <row r="6" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="382" t="s">
+      <c r="A6" s="383" t="s">
         <v>297</v>
       </c>
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
-      <c r="D6" s="383"/>
-      <c r="E6" s="383"/>
-      <c r="F6" s="383"/>
-      <c r="G6" s="383"/>
-      <c r="H6" s="383"/>
-      <c r="I6" s="383"/>
-      <c r="J6" s="383"/>
-      <c r="K6" s="383"/>
-      <c r="L6" s="384"/>
+      <c r="B6" s="384"/>
+      <c r="C6" s="384"/>
+      <c r="D6" s="384"/>
+      <c r="E6" s="384"/>
+      <c r="F6" s="384"/>
+      <c r="G6" s="384"/>
+      <c r="H6" s="384"/>
+      <c r="I6" s="384"/>
+      <c r="J6" s="384"/>
+      <c r="K6" s="384"/>
+      <c r="L6" s="385"/>
       <c r="N6" s="110"/>
       <c r="O6" s="110"/>
       <c r="P6" s="110"/>
@@ -17696,19 +19955,19 @@
     </row>
     <row r="7" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="214"/>
-      <c r="B7" s="383" t="s">
+      <c r="B7" s="384" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="383"/>
-      <c r="D7" s="383"/>
-      <c r="E7" s="383"/>
-      <c r="F7" s="383"/>
-      <c r="G7" s="383"/>
-      <c r="H7" s="383"/>
-      <c r="I7" s="383"/>
-      <c r="J7" s="383"/>
-      <c r="K7" s="383"/>
-      <c r="L7" s="384"/>
+      <c r="C7" s="384"/>
+      <c r="D7" s="384"/>
+      <c r="E7" s="384"/>
+      <c r="F7" s="384"/>
+      <c r="G7" s="384"/>
+      <c r="H7" s="384"/>
+      <c r="I7" s="384"/>
+      <c r="J7" s="384"/>
+      <c r="K7" s="384"/>
+      <c r="L7" s="385"/>
       <c r="N7" s="110"/>
       <c r="O7" s="110"/>
       <c r="P7" s="110"/>
@@ -17717,19 +19976,19 @@
     </row>
     <row r="8" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="215"/>
-      <c r="B8" s="398" t="s">
+      <c r="B8" s="399" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="398"/>
-      <c r="D8" s="398"/>
-      <c r="E8" s="398"/>
-      <c r="F8" s="398"/>
-      <c r="G8" s="398"/>
-      <c r="H8" s="398"/>
-      <c r="I8" s="398"/>
-      <c r="J8" s="398"/>
-      <c r="K8" s="398"/>
-      <c r="L8" s="399"/>
+      <c r="C8" s="399"/>
+      <c r="D8" s="399"/>
+      <c r="E8" s="399"/>
+      <c r="F8" s="399"/>
+      <c r="G8" s="399"/>
+      <c r="H8" s="399"/>
+      <c r="I8" s="399"/>
+      <c r="J8" s="399"/>
+      <c r="K8" s="399"/>
+      <c r="L8" s="400"/>
       <c r="N8" s="110"/>
       <c r="O8" s="110"/>
       <c r="P8" s="110"/>
@@ -17751,20 +20010,20 @@
       <c r="L9" s="110"/>
     </row>
     <row r="10" spans="1:18" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="400" t="s">
+      <c r="A10" s="401" t="s">
         <v>334</v>
       </c>
-      <c r="B10" s="401"/>
-      <c r="C10" s="401"/>
-      <c r="D10" s="401"/>
-      <c r="E10" s="401"/>
-      <c r="F10" s="401"/>
-      <c r="G10" s="401"/>
-      <c r="H10" s="401"/>
-      <c r="I10" s="401"/>
-      <c r="J10" s="401"/>
-      <c r="K10" s="401"/>
-      <c r="L10" s="402"/>
+      <c r="B10" s="402"/>
+      <c r="C10" s="402"/>
+      <c r="D10" s="402"/>
+      <c r="E10" s="402"/>
+      <c r="F10" s="402"/>
+      <c r="G10" s="402"/>
+      <c r="H10" s="402"/>
+      <c r="I10" s="402"/>
+      <c r="J10" s="402"/>
+      <c r="K10" s="402"/>
+      <c r="L10" s="403"/>
     </row>
     <row r="11" spans="1:18" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="344"/>
@@ -17784,19 +20043,19 @@
       <c r="A12" s="344" t="s">
         <v>335</v>
       </c>
-      <c r="B12" s="403" t="s">
+      <c r="B12" s="404" t="s">
         <v>478</v>
       </c>
-      <c r="C12" s="403"/>
-      <c r="D12" s="403"/>
-      <c r="E12" s="403"/>
-      <c r="F12" s="403"/>
-      <c r="G12" s="403"/>
-      <c r="H12" s="403"/>
-      <c r="I12" s="403"/>
-      <c r="J12" s="403"/>
-      <c r="K12" s="403"/>
-      <c r="L12" s="404"/>
+      <c r="C12" s="404"/>
+      <c r="D12" s="404"/>
+      <c r="E12" s="404"/>
+      <c r="F12" s="404"/>
+      <c r="G12" s="404"/>
+      <c r="H12" s="404"/>
+      <c r="I12" s="404"/>
+      <c r="J12" s="404"/>
+      <c r="K12" s="404"/>
+      <c r="L12" s="405"/>
     </row>
     <row r="13" spans="1:18" s="57" customFormat="1" ht="231" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="344"/>
@@ -17816,19 +20075,19 @@
       <c r="A14" s="235" t="s">
         <v>336</v>
       </c>
-      <c r="B14" s="353" t="s">
+      <c r="B14" s="354" t="s">
         <v>338</v>
       </c>
-      <c r="C14" s="353"/>
-      <c r="D14" s="353"/>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
-      <c r="G14" s="353"/>
-      <c r="H14" s="353"/>
-      <c r="I14" s="353"/>
-      <c r="J14" s="353"/>
-      <c r="K14" s="353"/>
-      <c r="L14" s="354"/>
+      <c r="C14" s="354"/>
+      <c r="D14" s="354"/>
+      <c r="E14" s="354"/>
+      <c r="F14" s="354"/>
+      <c r="G14" s="354"/>
+      <c r="H14" s="354"/>
+      <c r="I14" s="354"/>
+      <c r="J14" s="354"/>
+      <c r="K14" s="354"/>
+      <c r="L14" s="355"/>
     </row>
     <row r="15" spans="1:18" s="57" customFormat="1" ht="161.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="227"/>
@@ -17848,51 +20107,51 @@
       <c r="A16" s="235" t="s">
         <v>337</v>
       </c>
-      <c r="B16" s="353" t="s">
+      <c r="B16" s="354" t="s">
         <v>339</v>
       </c>
-      <c r="C16" s="353"/>
-      <c r="D16" s="353"/>
-      <c r="E16" s="353"/>
-      <c r="F16" s="353"/>
-      <c r="G16" s="353"/>
-      <c r="H16" s="353"/>
-      <c r="I16" s="353"/>
-      <c r="J16" s="353"/>
-      <c r="K16" s="353"/>
-      <c r="L16" s="354"/>
+      <c r="C16" s="354"/>
+      <c r="D16" s="354"/>
+      <c r="E16" s="354"/>
+      <c r="F16" s="354"/>
+      <c r="G16" s="354"/>
+      <c r="H16" s="354"/>
+      <c r="I16" s="354"/>
+      <c r="J16" s="354"/>
+      <c r="K16" s="354"/>
+      <c r="L16" s="355"/>
     </row>
     <row r="17" spans="1:14" s="57" customFormat="1" ht="90.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="227"/>
-      <c r="B17" s="355"/>
-      <c r="C17" s="355"/>
-      <c r="D17" s="355"/>
-      <c r="E17" s="355"/>
-      <c r="F17" s="355"/>
-      <c r="G17" s="355"/>
-      <c r="H17" s="355"/>
-      <c r="I17" s="355"/>
-      <c r="J17" s="355"/>
-      <c r="K17" s="355"/>
-      <c r="L17" s="356"/>
+      <c r="B17" s="356"/>
+      <c r="C17" s="356"/>
+      <c r="D17" s="356"/>
+      <c r="E17" s="356"/>
+      <c r="F17" s="356"/>
+      <c r="G17" s="356"/>
+      <c r="H17" s="356"/>
+      <c r="I17" s="356"/>
+      <c r="J17" s="356"/>
+      <c r="K17" s="356"/>
+      <c r="L17" s="357"/>
     </row>
     <row r="18" spans="1:14" s="56" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="235" t="s">
         <v>477</v>
       </c>
-      <c r="B18" s="353" t="s">
+      <c r="B18" s="354" t="s">
         <v>465</v>
       </c>
-      <c r="C18" s="353"/>
-      <c r="D18" s="353"/>
-      <c r="E18" s="353"/>
-      <c r="F18" s="353"/>
-      <c r="G18" s="353"/>
-      <c r="H18" s="353"/>
-      <c r="I18" s="353"/>
-      <c r="J18" s="353"/>
-      <c r="K18" s="353"/>
-      <c r="L18" s="354"/>
+      <c r="C18" s="354"/>
+      <c r="D18" s="354"/>
+      <c r="E18" s="354"/>
+      <c r="F18" s="354"/>
+      <c r="G18" s="354"/>
+      <c r="H18" s="354"/>
+      <c r="I18" s="354"/>
+      <c r="J18" s="354"/>
+      <c r="K18" s="354"/>
+      <c r="L18" s="355"/>
     </row>
     <row r="19" spans="1:14" s="57" customFormat="1" ht="269" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="227"/>
@@ -17909,12 +20168,12 @@
       <c r="L19" s="234"/>
     </row>
     <row r="20" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="351" t="s">
+      <c r="A20" s="352" t="s">
         <v>343</v>
       </c>
-      <c r="B20" s="352"/>
-      <c r="C20" s="352"/>
-      <c r="D20" s="352"/>
+      <c r="B20" s="353"/>
+      <c r="C20" s="353"/>
+      <c r="D20" s="353"/>
       <c r="E20" s="232" t="s">
         <v>344</v>
       </c>
@@ -17941,84 +20200,84 @@
       <c r="L21" s="110"/>
     </row>
     <row r="22" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="385" t="s">
+      <c r="A22" s="386" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="386"/>
-      <c r="C22" s="386"/>
-      <c r="D22" s="386"/>
-      <c r="E22" s="386"/>
-      <c r="F22" s="386"/>
-      <c r="G22" s="386"/>
-      <c r="H22" s="386"/>
-      <c r="I22" s="386"/>
-      <c r="J22" s="386"/>
-      <c r="K22" s="386"/>
-      <c r="L22" s="387"/>
+      <c r="B22" s="387"/>
+      <c r="C22" s="387"/>
+      <c r="D22" s="387"/>
+      <c r="E22" s="387"/>
+      <c r="F22" s="387"/>
+      <c r="G22" s="387"/>
+      <c r="H22" s="387"/>
+      <c r="I22" s="387"/>
+      <c r="J22" s="387"/>
+      <c r="K22" s="387"/>
+      <c r="L22" s="388"/>
     </row>
     <row r="23" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="388" t="s">
+      <c r="A23" s="389" t="s">
         <v>281</v>
       </c>
-      <c r="B23" s="389"/>
-      <c r="C23" s="389"/>
-      <c r="D23" s="389"/>
-      <c r="E23" s="389"/>
-      <c r="F23" s="389"/>
-      <c r="G23" s="389"/>
-      <c r="H23" s="389"/>
-      <c r="I23" s="389"/>
-      <c r="J23" s="389"/>
-      <c r="K23" s="389"/>
-      <c r="L23" s="390"/>
+      <c r="B23" s="390"/>
+      <c r="C23" s="390"/>
+      <c r="D23" s="390"/>
+      <c r="E23" s="390"/>
+      <c r="F23" s="390"/>
+      <c r="G23" s="390"/>
+      <c r="H23" s="390"/>
+      <c r="I23" s="390"/>
+      <c r="J23" s="390"/>
+      <c r="K23" s="390"/>
+      <c r="L23" s="391"/>
     </row>
     <row r="24" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="391" t="s">
+      <c r="A24" s="392" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="367"/>
-      <c r="C24" s="367"/>
-      <c r="D24" s="367"/>
-      <c r="E24" s="367"/>
-      <c r="F24" s="367"/>
-      <c r="G24" s="367"/>
-      <c r="H24" s="367"/>
-      <c r="I24" s="367"/>
-      <c r="J24" s="367"/>
-      <c r="K24" s="367"/>
-      <c r="L24" s="368"/>
+      <c r="B24" s="368"/>
+      <c r="C24" s="368"/>
+      <c r="D24" s="368"/>
+      <c r="E24" s="368"/>
+      <c r="F24" s="368"/>
+      <c r="G24" s="368"/>
+      <c r="H24" s="368"/>
+      <c r="I24" s="368"/>
+      <c r="J24" s="368"/>
+      <c r="K24" s="368"/>
+      <c r="L24" s="369"/>
     </row>
     <row r="25" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="391" t="s">
+      <c r="A25" s="392" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="367"/>
-      <c r="C25" s="367"/>
-      <c r="D25" s="367"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
-      <c r="G25" s="367"/>
-      <c r="H25" s="367"/>
-      <c r="I25" s="367"/>
-      <c r="J25" s="367"/>
-      <c r="K25" s="367"/>
-      <c r="L25" s="368"/>
+      <c r="B25" s="368"/>
+      <c r="C25" s="368"/>
+      <c r="D25" s="368"/>
+      <c r="E25" s="368"/>
+      <c r="F25" s="368"/>
+      <c r="G25" s="368"/>
+      <c r="H25" s="368"/>
+      <c r="I25" s="368"/>
+      <c r="J25" s="368"/>
+      <c r="K25" s="368"/>
+      <c r="L25" s="369"/>
     </row>
     <row r="26" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="392" t="s">
+      <c r="A26" s="393" t="s">
         <v>283</v>
       </c>
-      <c r="B26" s="393"/>
-      <c r="C26" s="393"/>
-      <c r="D26" s="393"/>
-      <c r="E26" s="393"/>
-      <c r="F26" s="393"/>
-      <c r="G26" s="393"/>
-      <c r="H26" s="393"/>
-      <c r="I26" s="393"/>
-      <c r="J26" s="393"/>
-      <c r="K26" s="393"/>
-      <c r="L26" s="394"/>
+      <c r="B26" s="394"/>
+      <c r="C26" s="394"/>
+      <c r="D26" s="394"/>
+      <c r="E26" s="394"/>
+      <c r="F26" s="394"/>
+      <c r="G26" s="394"/>
+      <c r="H26" s="394"/>
+      <c r="I26" s="394"/>
+      <c r="J26" s="394"/>
+      <c r="K26" s="394"/>
+      <c r="L26" s="395"/>
     </row>
     <row r="27" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="110"/>
@@ -18035,332 +20294,332 @@
       <c r="L27" s="110"/>
     </row>
     <row r="28" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="395" t="s">
+      <c r="A28" s="396" t="s">
         <v>279</v>
       </c>
-      <c r="B28" s="396"/>
-      <c r="C28" s="396"/>
-      <c r="D28" s="396"/>
-      <c r="E28" s="396"/>
-      <c r="F28" s="396"/>
-      <c r="G28" s="396"/>
-      <c r="H28" s="396"/>
-      <c r="I28" s="396"/>
-      <c r="J28" s="396"/>
-      <c r="K28" s="396"/>
-      <c r="L28" s="397"/>
+      <c r="B28" s="397"/>
+      <c r="C28" s="397"/>
+      <c r="D28" s="397"/>
+      <c r="E28" s="397"/>
+      <c r="F28" s="397"/>
+      <c r="G28" s="397"/>
+      <c r="H28" s="397"/>
+      <c r="I28" s="397"/>
+      <c r="J28" s="397"/>
+      <c r="K28" s="397"/>
+      <c r="L28" s="398"/>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="374" t="s">
+      <c r="A29" s="375" t="s">
         <v>175</v>
       </c>
-      <c r="B29" s="375"/>
-      <c r="C29" s="375"/>
-      <c r="D29" s="375"/>
-      <c r="E29" s="375"/>
-      <c r="F29" s="375"/>
-      <c r="G29" s="375"/>
-      <c r="H29" s="375"/>
-      <c r="I29" s="375"/>
-      <c r="J29" s="375"/>
-      <c r="K29" s="375"/>
-      <c r="L29" s="376"/>
+      <c r="B29" s="376"/>
+      <c r="C29" s="376"/>
+      <c r="D29" s="376"/>
+      <c r="E29" s="376"/>
+      <c r="F29" s="376"/>
+      <c r="G29" s="376"/>
+      <c r="H29" s="376"/>
+      <c r="I29" s="376"/>
+      <c r="J29" s="376"/>
+      <c r="K29" s="376"/>
+      <c r="L29" s="377"/>
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="209">
         <v>1</v>
       </c>
-      <c r="B30" s="360" t="s">
+      <c r="B30" s="361" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="360"/>
-      <c r="D30" s="360"/>
-      <c r="E30" s="360"/>
-      <c r="F30" s="360"/>
-      <c r="G30" s="360"/>
-      <c r="H30" s="360"/>
-      <c r="I30" s="360"/>
-      <c r="J30" s="360"/>
-      <c r="K30" s="360"/>
-      <c r="L30" s="361"/>
+      <c r="C30" s="361"/>
+      <c r="D30" s="361"/>
+      <c r="E30" s="361"/>
+      <c r="F30" s="361"/>
+      <c r="G30" s="361"/>
+      <c r="H30" s="361"/>
+      <c r="I30" s="361"/>
+      <c r="J30" s="361"/>
+      <c r="K30" s="361"/>
+      <c r="L30" s="362"/>
     </row>
     <row r="31" spans="1:14" s="57" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="209">
         <v>2</v>
       </c>
-      <c r="B31" s="360" t="s">
+      <c r="B31" s="361" t="s">
         <v>275</v>
       </c>
-      <c r="C31" s="360"/>
-      <c r="D31" s="360"/>
-      <c r="E31" s="360"/>
-      <c r="F31" s="360"/>
-      <c r="G31" s="360"/>
-      <c r="H31" s="360"/>
-      <c r="I31" s="360"/>
-      <c r="J31" s="360"/>
-      <c r="K31" s="360"/>
-      <c r="L31" s="361"/>
+      <c r="C31" s="361"/>
+      <c r="D31" s="361"/>
+      <c r="E31" s="361"/>
+      <c r="F31" s="361"/>
+      <c r="G31" s="361"/>
+      <c r="H31" s="361"/>
+      <c r="I31" s="361"/>
+      <c r="J31" s="361"/>
+      <c r="K31" s="361"/>
+      <c r="L31" s="362"/>
       <c r="N31" s="104"/>
     </row>
     <row r="32" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="209">
         <v>3</v>
       </c>
-      <c r="B32" s="360" t="s">
+      <c r="B32" s="361" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="360"/>
-      <c r="D32" s="360"/>
-      <c r="E32" s="360"/>
-      <c r="F32" s="360"/>
-      <c r="G32" s="360"/>
-      <c r="H32" s="360"/>
-      <c r="I32" s="360"/>
-      <c r="J32" s="360"/>
-      <c r="K32" s="360"/>
-      <c r="L32" s="361"/>
+      <c r="C32" s="361"/>
+      <c r="D32" s="361"/>
+      <c r="E32" s="361"/>
+      <c r="F32" s="361"/>
+      <c r="G32" s="361"/>
+      <c r="H32" s="361"/>
+      <c r="I32" s="361"/>
+      <c r="J32" s="361"/>
+      <c r="K32" s="361"/>
+      <c r="L32" s="362"/>
       <c r="N32" s="104"/>
     </row>
     <row r="33" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="209">
         <v>4</v>
       </c>
-      <c r="B33" s="360" t="s">
+      <c r="B33" s="361" t="s">
         <v>284</v>
       </c>
-      <c r="C33" s="360"/>
-      <c r="D33" s="360"/>
-      <c r="E33" s="360"/>
-      <c r="F33" s="360"/>
-      <c r="G33" s="360"/>
-      <c r="H33" s="360"/>
-      <c r="I33" s="360"/>
-      <c r="J33" s="360"/>
-      <c r="K33" s="360"/>
-      <c r="L33" s="361"/>
+      <c r="C33" s="361"/>
+      <c r="D33" s="361"/>
+      <c r="E33" s="361"/>
+      <c r="F33" s="361"/>
+      <c r="G33" s="361"/>
+      <c r="H33" s="361"/>
+      <c r="I33" s="361"/>
+      <c r="J33" s="361"/>
+      <c r="K33" s="361"/>
+      <c r="L33" s="362"/>
       <c r="N33" s="104"/>
     </row>
     <row r="34" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="209">
         <v>5</v>
       </c>
-      <c r="B34" s="360" t="s">
+      <c r="B34" s="361" t="s">
         <v>168</v>
       </c>
-      <c r="C34" s="360"/>
-      <c r="D34" s="360"/>
-      <c r="E34" s="360"/>
-      <c r="F34" s="360"/>
-      <c r="G34" s="360"/>
-      <c r="H34" s="360"/>
-      <c r="I34" s="360"/>
-      <c r="J34" s="360"/>
-      <c r="K34" s="360"/>
-      <c r="L34" s="361"/>
+      <c r="C34" s="361"/>
+      <c r="D34" s="361"/>
+      <c r="E34" s="361"/>
+      <c r="F34" s="361"/>
+      <c r="G34" s="361"/>
+      <c r="H34" s="361"/>
+      <c r="I34" s="361"/>
+      <c r="J34" s="361"/>
+      <c r="K34" s="361"/>
+      <c r="L34" s="362"/>
       <c r="N34" s="104"/>
     </row>
     <row r="35" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="209"/>
-      <c r="B35" s="360" t="s">
+      <c r="B35" s="361" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="360"/>
-      <c r="D35" s="360"/>
-      <c r="E35" s="360"/>
-      <c r="F35" s="360"/>
-      <c r="G35" s="360"/>
-      <c r="H35" s="360"/>
-      <c r="I35" s="360"/>
-      <c r="J35" s="360"/>
-      <c r="K35" s="360"/>
-      <c r="L35" s="361"/>
+      <c r="C35" s="361"/>
+      <c r="D35" s="361"/>
+      <c r="E35" s="361"/>
+      <c r="F35" s="361"/>
+      <c r="G35" s="361"/>
+      <c r="H35" s="361"/>
+      <c r="I35" s="361"/>
+      <c r="J35" s="361"/>
+      <c r="K35" s="361"/>
+      <c r="L35" s="362"/>
       <c r="N35" s="104"/>
     </row>
     <row r="36" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="209"/>
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
-      <c r="G36" s="360"/>
-      <c r="H36" s="360"/>
-      <c r="I36" s="360"/>
-      <c r="J36" s="360"/>
-      <c r="K36" s="360"/>
-      <c r="L36" s="361"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
+      <c r="G36" s="361"/>
+      <c r="H36" s="361"/>
+      <c r="I36" s="361"/>
+      <c r="J36" s="361"/>
+      <c r="K36" s="361"/>
+      <c r="L36" s="362"/>
       <c r="N36" s="104"/>
     </row>
     <row r="37" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="369" t="s">
+      <c r="A37" s="370" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="370"/>
-      <c r="C37" s="370"/>
-      <c r="D37" s="370"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
-      <c r="G37" s="370"/>
-      <c r="H37" s="370"/>
-      <c r="I37" s="370"/>
-      <c r="J37" s="370"/>
-      <c r="K37" s="370"/>
-      <c r="L37" s="371"/>
+      <c r="B37" s="371"/>
+      <c r="C37" s="371"/>
+      <c r="D37" s="371"/>
+      <c r="E37" s="371"/>
+      <c r="F37" s="371"/>
+      <c r="G37" s="371"/>
+      <c r="H37" s="371"/>
+      <c r="I37" s="371"/>
+      <c r="J37" s="371"/>
+      <c r="K37" s="371"/>
+      <c r="L37" s="372"/>
       <c r="N37" s="104"/>
     </row>
     <row r="38" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="209">
         <v>1</v>
       </c>
-      <c r="B38" s="360" t="s">
+      <c r="B38" s="361" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="360"/>
-      <c r="D38" s="360"/>
-      <c r="E38" s="360"/>
-      <c r="F38" s="360"/>
-      <c r="G38" s="360"/>
-      <c r="H38" s="360"/>
-      <c r="I38" s="360"/>
-      <c r="J38" s="360"/>
-      <c r="K38" s="360"/>
-      <c r="L38" s="361"/>
+      <c r="C38" s="361"/>
+      <c r="D38" s="361"/>
+      <c r="E38" s="361"/>
+      <c r="F38" s="361"/>
+      <c r="G38" s="361"/>
+      <c r="H38" s="361"/>
+      <c r="I38" s="361"/>
+      <c r="J38" s="361"/>
+      <c r="K38" s="361"/>
+      <c r="L38" s="362"/>
       <c r="N38" s="104"/>
     </row>
     <row r="39" spans="1:14" s="57" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="209"/>
-      <c r="B39" s="358" t="s">
+      <c r="B39" s="359" t="s">
         <v>426</v>
       </c>
-      <c r="C39" s="358"/>
-      <c r="D39" s="358"/>
-      <c r="E39" s="358"/>
-      <c r="F39" s="358"/>
-      <c r="G39" s="358"/>
-      <c r="H39" s="358"/>
-      <c r="I39" s="358"/>
-      <c r="J39" s="358"/>
-      <c r="K39" s="358"/>
-      <c r="L39" s="359"/>
+      <c r="C39" s="359"/>
+      <c r="D39" s="359"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
+      <c r="G39" s="359"/>
+      <c r="H39" s="359"/>
+      <c r="I39" s="359"/>
+      <c r="J39" s="359"/>
+      <c r="K39" s="359"/>
+      <c r="L39" s="360"/>
       <c r="N39" s="104"/>
     </row>
     <row r="40" spans="1:14" s="57" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="209">
         <v>2</v>
       </c>
-      <c r="B40" s="360" t="s">
+      <c r="B40" s="361" t="s">
         <v>278</v>
       </c>
-      <c r="C40" s="360"/>
-      <c r="D40" s="360"/>
-      <c r="E40" s="360"/>
-      <c r="F40" s="360"/>
-      <c r="G40" s="360"/>
-      <c r="H40" s="360"/>
-      <c r="I40" s="360"/>
-      <c r="J40" s="360"/>
-      <c r="K40" s="360"/>
-      <c r="L40" s="361"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
+      <c r="G40" s="361"/>
+      <c r="H40" s="361"/>
+      <c r="I40" s="361"/>
+      <c r="J40" s="361"/>
+      <c r="K40" s="361"/>
+      <c r="L40" s="362"/>
       <c r="N40" s="104"/>
     </row>
     <row r="41" spans="1:14" s="57" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="209">
         <v>3</v>
       </c>
-      <c r="B41" s="360" t="s">
+      <c r="B41" s="361" t="s">
         <v>475</v>
       </c>
-      <c r="C41" s="360"/>
-      <c r="D41" s="360"/>
-      <c r="E41" s="360"/>
-      <c r="F41" s="360"/>
-      <c r="G41" s="360"/>
-      <c r="H41" s="360"/>
-      <c r="I41" s="360"/>
-      <c r="J41" s="360"/>
-      <c r="K41" s="360"/>
-      <c r="L41" s="361"/>
+      <c r="C41" s="361"/>
+      <c r="D41" s="361"/>
+      <c r="E41" s="361"/>
+      <c r="F41" s="361"/>
+      <c r="G41" s="361"/>
+      <c r="H41" s="361"/>
+      <c r="I41" s="361"/>
+      <c r="J41" s="361"/>
+      <c r="K41" s="361"/>
+      <c r="L41" s="362"/>
       <c r="N41" s="104"/>
     </row>
     <row r="42" spans="1:14" s="57" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="209">
         <v>4</v>
       </c>
-      <c r="B42" s="360" t="s">
+      <c r="B42" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="C42" s="360"/>
-      <c r="D42" s="360"/>
-      <c r="E42" s="360"/>
-      <c r="F42" s="360"/>
-      <c r="G42" s="360"/>
-      <c r="H42" s="360"/>
-      <c r="I42" s="360"/>
-      <c r="J42" s="360"/>
-      <c r="K42" s="360"/>
-      <c r="L42" s="361"/>
+      <c r="C42" s="361"/>
+      <c r="D42" s="361"/>
+      <c r="E42" s="361"/>
+      <c r="F42" s="361"/>
+      <c r="G42" s="361"/>
+      <c r="H42" s="361"/>
+      <c r="I42" s="361"/>
+      <c r="J42" s="361"/>
+      <c r="K42" s="361"/>
+      <c r="L42" s="362"/>
       <c r="N42" s="104"/>
     </row>
     <row r="43" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="209">
         <v>5</v>
       </c>
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="359" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
-      <c r="G43" s="358"/>
-      <c r="H43" s="358"/>
-      <c r="I43" s="358"/>
-      <c r="J43" s="358"/>
-      <c r="K43" s="358"/>
-      <c r="L43" s="359"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+      <c r="G43" s="359"/>
+      <c r="H43" s="359"/>
+      <c r="I43" s="359"/>
+      <c r="J43" s="359"/>
+      <c r="K43" s="359"/>
+      <c r="L43" s="360"/>
       <c r="N43" s="104"/>
     </row>
     <row r="44" spans="1:14" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="209">
         <v>6</v>
       </c>
-      <c r="B44" s="358" t="s">
+      <c r="B44" s="359" t="s">
         <v>476</v>
       </c>
-      <c r="C44" s="358"/>
-      <c r="D44" s="358"/>
-      <c r="E44" s="358"/>
-      <c r="F44" s="358"/>
-      <c r="G44" s="358"/>
-      <c r="H44" s="358"/>
-      <c r="I44" s="358"/>
-      <c r="J44" s="358"/>
-      <c r="K44" s="358"/>
-      <c r="L44" s="359"/>
+      <c r="C44" s="359"/>
+      <c r="D44" s="359"/>
+      <c r="E44" s="359"/>
+      <c r="F44" s="359"/>
+      <c r="G44" s="359"/>
+      <c r="H44" s="359"/>
+      <c r="I44" s="359"/>
+      <c r="J44" s="359"/>
+      <c r="K44" s="359"/>
+      <c r="L44" s="360"/>
       <c r="N44" s="104"/>
     </row>
     <row r="45" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="209">
         <v>7</v>
       </c>
-      <c r="B45" s="360" t="s">
+      <c r="B45" s="361" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="360"/>
-      <c r="D45" s="360"/>
-      <c r="E45" s="360"/>
-      <c r="F45" s="360"/>
-      <c r="G45" s="360"/>
-      <c r="H45" s="360"/>
-      <c r="I45" s="360"/>
-      <c r="J45" s="360"/>
-      <c r="K45" s="360"/>
-      <c r="L45" s="361"/>
+      <c r="C45" s="361"/>
+      <c r="D45" s="361"/>
+      <c r="E45" s="361"/>
+      <c r="F45" s="361"/>
+      <c r="G45" s="361"/>
+      <c r="H45" s="361"/>
+      <c r="I45" s="361"/>
+      <c r="J45" s="361"/>
+      <c r="K45" s="361"/>
+      <c r="L45" s="362"/>
     </row>
     <row r="46" spans="1:14" s="57" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="209"/>
@@ -18377,56 +20636,56 @@
       <c r="L46" s="211"/>
     </row>
     <row r="47" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="369" t="s">
+      <c r="A47" s="370" t="s">
         <v>273</v>
       </c>
-      <c r="B47" s="370"/>
-      <c r="C47" s="370"/>
-      <c r="D47" s="370"/>
-      <c r="E47" s="370"/>
-      <c r="F47" s="370"/>
-      <c r="G47" s="370"/>
-      <c r="H47" s="370"/>
-      <c r="I47" s="370"/>
-      <c r="J47" s="370"/>
-      <c r="K47" s="370"/>
-      <c r="L47" s="371"/>
+      <c r="B47" s="371"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
+      <c r="G47" s="371"/>
+      <c r="H47" s="371"/>
+      <c r="I47" s="371"/>
+      <c r="J47" s="371"/>
+      <c r="K47" s="371"/>
+      <c r="L47" s="372"/>
     </row>
     <row r="48" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="212" t="s">
         <v>271</v>
       </c>
-      <c r="B48" s="360" t="s">
+      <c r="B48" s="361" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="360"/>
-      <c r="D48" s="360"/>
-      <c r="E48" s="360"/>
-      <c r="F48" s="360"/>
-      <c r="G48" s="360"/>
-      <c r="H48" s="360"/>
-      <c r="I48" s="360"/>
-      <c r="J48" s="360"/>
-      <c r="K48" s="360"/>
-      <c r="L48" s="361"/>
+      <c r="C48" s="361"/>
+      <c r="D48" s="361"/>
+      <c r="E48" s="361"/>
+      <c r="F48" s="361"/>
+      <c r="G48" s="361"/>
+      <c r="H48" s="361"/>
+      <c r="I48" s="361"/>
+      <c r="J48" s="361"/>
+      <c r="K48" s="361"/>
+      <c r="L48" s="362"/>
     </row>
     <row r="49" spans="1:12" s="57" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="B49" s="362" t="s">
+      <c r="B49" s="363" t="s">
         <v>274</v>
       </c>
-      <c r="C49" s="362"/>
-      <c r="D49" s="362"/>
-      <c r="E49" s="362"/>
-      <c r="F49" s="362"/>
-      <c r="G49" s="362"/>
-      <c r="H49" s="362"/>
-      <c r="I49" s="362"/>
-      <c r="J49" s="362"/>
-      <c r="K49" s="362"/>
-      <c r="L49" s="363"/>
+      <c r="C49" s="363"/>
+      <c r="D49" s="363"/>
+      <c r="E49" s="363"/>
+      <c r="F49" s="363"/>
+      <c r="G49" s="363"/>
+      <c r="H49" s="363"/>
+      <c r="I49" s="363"/>
+      <c r="J49" s="363"/>
+      <c r="K49" s="363"/>
+      <c r="L49" s="364"/>
     </row>
     <row r="50" spans="1:12" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="157"/>
@@ -18443,20 +20702,20 @@
       <c r="L50" s="110"/>
     </row>
     <row r="51" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="364" t="s">
+      <c r="A51" s="365" t="s">
         <v>200</v>
       </c>
-      <c r="B51" s="365"/>
-      <c r="C51" s="365"/>
-      <c r="D51" s="365"/>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
-      <c r="G51" s="365"/>
-      <c r="H51" s="365"/>
-      <c r="I51" s="365"/>
-      <c r="J51" s="365"/>
-      <c r="K51" s="365"/>
-      <c r="L51" s="366"/>
+      <c r="B51" s="366"/>
+      <c r="C51" s="366"/>
+      <c r="D51" s="366"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
+      <c r="G51" s="366"/>
+      <c r="H51" s="366"/>
+      <c r="I51" s="366"/>
+      <c r="J51" s="366"/>
+      <c r="K51" s="366"/>
+      <c r="L51" s="367"/>
     </row>
     <row r="52" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="216" t="s">
@@ -18544,126 +20803,126 @@
       <c r="B57" s="165" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="367" t="s">
+      <c r="C57" s="368" t="s">
         <v>262</v>
       </c>
-      <c r="D57" s="367"/>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
-      <c r="G57" s="367"/>
-      <c r="H57" s="367"/>
-      <c r="I57" s="367"/>
-      <c r="J57" s="367"/>
-      <c r="K57" s="367"/>
-      <c r="L57" s="368"/>
+      <c r="D57" s="368"/>
+      <c r="E57" s="368"/>
+      <c r="F57" s="368"/>
+      <c r="G57" s="368"/>
+      <c r="H57" s="368"/>
+      <c r="I57" s="368"/>
+      <c r="J57" s="368"/>
+      <c r="K57" s="368"/>
+      <c r="L57" s="369"/>
     </row>
     <row r="58" spans="1:12" s="56" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="164"/>
       <c r="B58" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="C58" s="367" t="s">
+      <c r="C58" s="368" t="s">
         <v>264</v>
       </c>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
-      <c r="G58" s="367"/>
-      <c r="H58" s="367"/>
-      <c r="I58" s="367"/>
-      <c r="J58" s="367"/>
-      <c r="K58" s="367"/>
-      <c r="L58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
+      <c r="G58" s="368"/>
+      <c r="H58" s="368"/>
+      <c r="I58" s="368"/>
+      <c r="J58" s="368"/>
+      <c r="K58" s="368"/>
+      <c r="L58" s="369"/>
     </row>
     <row r="59" spans="1:12" s="56" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="164"/>
       <c r="B59" s="165" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="367" t="s">
+      <c r="C59" s="368" t="s">
         <v>328</v>
       </c>
-      <c r="D59" s="367"/>
-      <c r="E59" s="367"/>
-      <c r="F59" s="367"/>
-      <c r="G59" s="367"/>
-      <c r="H59" s="367"/>
-      <c r="I59" s="367"/>
-      <c r="J59" s="367"/>
-      <c r="K59" s="367"/>
-      <c r="L59" s="368"/>
+      <c r="D59" s="368"/>
+      <c r="E59" s="368"/>
+      <c r="F59" s="368"/>
+      <c r="G59" s="368"/>
+      <c r="H59" s="368"/>
+      <c r="I59" s="368"/>
+      <c r="J59" s="368"/>
+      <c r="K59" s="368"/>
+      <c r="L59" s="369"/>
     </row>
     <row r="60" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="164"/>
       <c r="B60" s="165" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="367" t="s">
+      <c r="C60" s="368" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="367"/>
-      <c r="E60" s="367"/>
-      <c r="F60" s="367"/>
-      <c r="G60" s="367"/>
-      <c r="H60" s="367"/>
-      <c r="I60" s="367"/>
-      <c r="J60" s="367"/>
-      <c r="K60" s="367"/>
-      <c r="L60" s="368"/>
+      <c r="D60" s="368"/>
+      <c r="E60" s="368"/>
+      <c r="F60" s="368"/>
+      <c r="G60" s="368"/>
+      <c r="H60" s="368"/>
+      <c r="I60" s="368"/>
+      <c r="J60" s="368"/>
+      <c r="K60" s="368"/>
+      <c r="L60" s="369"/>
     </row>
     <row r="61" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="164"/>
       <c r="B61" s="165" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="367" t="s">
+      <c r="C61" s="368" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="367"/>
-      <c r="E61" s="367"/>
-      <c r="F61" s="367"/>
-      <c r="G61" s="367"/>
-      <c r="H61" s="367"/>
-      <c r="I61" s="367"/>
-      <c r="J61" s="367"/>
-      <c r="K61" s="367"/>
-      <c r="L61" s="368"/>
+      <c r="D61" s="368"/>
+      <c r="E61" s="368"/>
+      <c r="F61" s="368"/>
+      <c r="G61" s="368"/>
+      <c r="H61" s="368"/>
+      <c r="I61" s="368"/>
+      <c r="J61" s="368"/>
+      <c r="K61" s="368"/>
+      <c r="L61" s="369"/>
     </row>
     <row r="62" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="164"/>
       <c r="B62" s="165" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="367" t="s">
+      <c r="C62" s="368" t="s">
         <v>466</v>
       </c>
-      <c r="D62" s="372"/>
-      <c r="E62" s="372"/>
-      <c r="F62" s="372"/>
-      <c r="G62" s="372"/>
-      <c r="H62" s="372"/>
-      <c r="I62" s="372"/>
-      <c r="J62" s="372"/>
-      <c r="K62" s="372"/>
-      <c r="L62" s="373"/>
+      <c r="D62" s="373"/>
+      <c r="E62" s="373"/>
+      <c r="F62" s="373"/>
+      <c r="G62" s="373"/>
+      <c r="H62" s="373"/>
+      <c r="I62" s="373"/>
+      <c r="J62" s="373"/>
+      <c r="K62" s="373"/>
+      <c r="L62" s="374"/>
     </row>
     <row r="63" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="164"/>
       <c r="B63" s="165" t="s">
         <v>393</v>
       </c>
-      <c r="C63" s="367" t="s">
+      <c r="C63" s="368" t="s">
         <v>394</v>
       </c>
-      <c r="D63" s="367"/>
-      <c r="E63" s="367"/>
-      <c r="F63" s="367"/>
-      <c r="G63" s="367"/>
-      <c r="H63" s="367"/>
-      <c r="I63" s="367"/>
-      <c r="J63" s="367"/>
-      <c r="K63" s="367"/>
-      <c r="L63" s="368"/>
+      <c r="D63" s="368"/>
+      <c r="E63" s="368"/>
+      <c r="F63" s="368"/>
+      <c r="G63" s="368"/>
+      <c r="H63" s="368"/>
+      <c r="I63" s="368"/>
+      <c r="J63" s="368"/>
+      <c r="K63" s="368"/>
+      <c r="L63" s="369"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="164"/>
@@ -18781,20 +21040,20 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="357" t="s">
+      <c r="A85" s="358" t="s">
         <v>397</v>
       </c>
-      <c r="B85" s="357"/>
-      <c r="C85" s="357"/>
-      <c r="D85" s="357"/>
-      <c r="E85" s="357"/>
-      <c r="F85" s="357"/>
-      <c r="G85" s="357"/>
-      <c r="H85" s="357"/>
-      <c r="I85" s="357"/>
-      <c r="J85" s="357"/>
-      <c r="K85" s="357"/>
-      <c r="L85" s="357"/>
+      <c r="B85" s="358"/>
+      <c r="C85" s="358"/>
+      <c r="D85" s="358"/>
+      <c r="E85" s="358"/>
+      <c r="F85" s="358"/>
+      <c r="G85" s="358"/>
+      <c r="H85" s="358"/>
+      <c r="I85" s="358"/>
+      <c r="J85" s="358"/>
+      <c r="K85" s="358"/>
+      <c r="L85" s="358"/>
     </row>
     <row r="90" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="91" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -18867,6 +21126,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40DCCE44-B8F9-46D8-A6D4-13802D9B3503}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18881,82 +21141,82 @@
       </c>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="449" t="s">
+      <c r="A3" s="450" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="449"/>
-      <c r="C3" s="449"/>
+      <c r="B3" s="450"/>
+      <c r="C3" s="450"/>
       <c r="D3" s="125" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="450" t="s">
+      <c r="A4" s="451" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="450"/>
-      <c r="C4" s="450"/>
+      <c r="B4" s="451"/>
+      <c r="C4" s="451"/>
       <c r="D4" s="172" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="454" t="s">
+      <c r="A5" s="455" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="451"/>
-      <c r="C5" s="451"/>
+      <c r="B5" s="452"/>
+      <c r="C5" s="452"/>
       <c r="D5" s="173" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="452" t="s">
+      <c r="A6" s="453" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="452"/>
-      <c r="C6" s="452"/>
+      <c r="B6" s="453"/>
+      <c r="C6" s="453"/>
       <c r="D6" s="174" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="453" t="s">
+      <c r="A7" s="454" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="453"/>
-      <c r="C7" s="453"/>
+      <c r="B7" s="454"/>
+      <c r="C7" s="454"/>
       <c r="D7" s="175" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="450" t="s">
+      <c r="A11" s="451" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="450"/>
-      <c r="C11" s="450"/>
+      <c r="B11" s="451"/>
+      <c r="C11" s="451"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="451" t="s">
+      <c r="A12" s="452" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="451"/>
-      <c r="C12" s="451"/>
+      <c r="B12" s="452"/>
+      <c r="C12" s="452"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="452" t="s">
+      <c r="A13" s="453" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="452"/>
-      <c r="C13" s="452"/>
+      <c r="B13" s="453"/>
+      <c r="C13" s="453"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="453" t="s">
+      <c r="A14" s="454" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="453"/>
-      <c r="C14" s="453"/>
+      <c r="B14" s="454"/>
+      <c r="C14" s="454"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -18976,6 +21236,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1107FA9C-0500-8E4A-A9C4-1B25444775C1}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19203,7 +21464,462 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EC9312-1D6A-C146-B06E-16E6A54035B4}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="351" t="str">
+        <f>_xlfn.CONCAT("Chosen Protect Elevation: ",Master!B20, " ft")</f>
+        <v>Chosen Protect Elevation:  ft</v>
+      </c>
+      <c r="B2" s="95">
+        <f>Master!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="95">
+        <f>Master!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="95">
+        <f>Master!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="95">
+        <f>Master!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="95">
+        <f>Master!$C$20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" s="95">
+        <v>10.857008</v>
+      </c>
+      <c r="C3" s="95">
+        <v>10.857008</v>
+      </c>
+      <c r="D3" s="95">
+        <v>10.857008</v>
+      </c>
+      <c r="E3" s="95">
+        <v>10.857008</v>
+      </c>
+      <c r="F3" s="95">
+        <v>10.857008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B4" s="95">
+        <v>2.2231700000000001</v>
+      </c>
+      <c r="C4" s="95">
+        <v>2.2231700000000001</v>
+      </c>
+      <c r="D4" s="95">
+        <v>2.2231700000000001</v>
+      </c>
+      <c r="E4" s="95">
+        <v>2.2231700000000001</v>
+      </c>
+      <c r="F4" s="95">
+        <v>2.2231700000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B5" s="95">
+        <v>3.1563530000000002</v>
+      </c>
+      <c r="C5" s="95">
+        <v>3.1563530000000002</v>
+      </c>
+      <c r="D5" s="95">
+        <v>3.1563530000000002</v>
+      </c>
+      <c r="E5" s="95">
+        <v>3.1563530000000002</v>
+      </c>
+      <c r="F5" s="95">
+        <v>3.1563530000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="458" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="459"/>
+      <c r="C6" s="459"/>
+      <c r="D6" s="459"/>
+      <c r="E6" s="459"/>
+      <c r="F6" s="459"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="460" t="s">
+        <v>485</v>
+      </c>
+      <c r="C7" s="460"/>
+      <c r="D7" s="460"/>
+      <c r="E7" s="460"/>
+      <c r="F7" s="460"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="17" t="str">
+        <f>Master!C83</f>
+        <v/>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f>Master!D83</f>
+        <v/>
+      </c>
+      <c r="D9" s="17" t="str">
+        <f>Master!E83</f>
+        <v/>
+      </c>
+      <c r="E9" s="17" t="str">
+        <f>Master!F83</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>Master!G83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="17" t="str">
+        <f>Master!C93</f>
+        <v/>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f>Master!D93</f>
+        <v/>
+      </c>
+      <c r="D10" s="17" t="str">
+        <f>Master!E93</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="str">
+        <f>Master!F93</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f>Master!G93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="17" t="str">
+        <f>Master!C103</f>
+        <v/>
+      </c>
+      <c r="C11" s="17" t="str">
+        <f>Master!D103</f>
+        <v/>
+      </c>
+      <c r="D11" s="17" t="str">
+        <f>Master!E103</f>
+        <v/>
+      </c>
+      <c r="E11" s="17" t="str">
+        <f>Master!F103</f>
+        <v/>
+      </c>
+      <c r="F11" s="17" t="str">
+        <f>Master!G103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="17" t="str" cm="1">
+        <f t="array" ref="B12:F12">Master!C113:G113</f>
+        <v/>
+      </c>
+      <c r="C12" s="17" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="17" t="str">
+        <v/>
+      </c>
+      <c r="E12" s="17" t="str">
+        <v/>
+      </c>
+      <c r="F12" s="17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B13" s="17" t="str" cm="1">
+        <f t="array" ref="B13:F13">Master!C123:G123</f>
+        <v/>
+      </c>
+      <c r="C13" s="17" t="str">
+        <v/>
+      </c>
+      <c r="D13" s="17" t="str">
+        <v/>
+      </c>
+      <c r="E13" s="17" t="str">
+        <v/>
+      </c>
+      <c r="F13" s="17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="51" t="s">
+        <v>486</v>
+      </c>
+      <c r="B14" s="17" t="str">
+        <f>Master!C73</f>
+        <v/>
+      </c>
+      <c r="C14" s="17" t="str">
+        <f>Master!D73</f>
+        <v/>
+      </c>
+      <c r="D14" s="17" t="str">
+        <f>Master!E73</f>
+        <v/>
+      </c>
+      <c r="E14" s="17" t="str">
+        <f>Master!F73</f>
+        <v/>
+      </c>
+      <c r="F14" s="17" t="str">
+        <f>Master!G73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="460" t="s">
+        <v>487</v>
+      </c>
+      <c r="C16" s="460"/>
+      <c r="D16" s="460"/>
+      <c r="E16" s="460"/>
+      <c r="F16" s="460"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" t="str">
+        <f>IF(OR(B9=0, B9=""), "", $A9 &amp; ", " &amp; TEXT(B9, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <f>IF(OR(C9=0, C9=""), "", $A9 &amp; ", " &amp; TEXT(C9, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" ref="D18:F18" si="0">IF(OR(D9=0, D9=""), "", $A9 &amp; ", " &amp; TEXT(D9, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" t="str">
+        <f t="shared" ref="B19:F19" si="1">IF(OR(B10=0, B10=""), "", $A10 &amp; ", " &amp; TEXT(B10, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" t="str">
+        <f t="shared" ref="B20:F20" si="2">IF(OR(B11=0, B11=""), "", $A11 &amp; ", " &amp; TEXT(B11, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f t="shared" ref="B21:F21" si="3">IF(OR(B12=0, B12=""), "", $A12 &amp; ", " &amp; TEXT(B12, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22" t="str">
+        <f t="shared" ref="B22:F22" si="4">IF(OR(B13=0, B13=""), "", $A13 &amp; ", " &amp; TEXT(B13, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23" t="str">
+        <f t="shared" ref="B23:F23" si="5">IF(OR(B14=0, B14=""), "", $A14 &amp; ", " &amp; TEXT(B14, "0.0"))</f>
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B16:F16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD0CEE0E-0924-954A-8EB1-099546BF662D}">
+  <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19217,28 +21933,28 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="455" t="s">
+      <c r="A2" s="456" t="s">
         <v>420</v>
       </c>
-      <c r="B2" s="456"/>
-      <c r="C2" s="456"/>
-      <c r="D2" s="456"/>
-      <c r="E2" s="456"/>
-      <c r="F2" s="456"/>
-      <c r="G2" s="456"/>
-      <c r="H2" s="456"/>
-      <c r="I2" s="456"/>
-      <c r="J2" s="456"/>
-      <c r="K2" s="456"/>
-      <c r="L2" s="456"/>
-      <c r="M2" s="456"/>
-      <c r="N2" s="456"/>
-      <c r="O2" s="456"/>
-      <c r="P2" s="456"/>
-      <c r="Q2" s="456"/>
-      <c r="R2" s="456"/>
-      <c r="S2" s="456"/>
-      <c r="T2" s="456"/>
+      <c r="B2" s="457"/>
+      <c r="C2" s="457"/>
+      <c r="D2" s="457"/>
+      <c r="E2" s="457"/>
+      <c r="F2" s="457"/>
+      <c r="G2" s="457"/>
+      <c r="H2" s="457"/>
+      <c r="I2" s="457"/>
+      <c r="J2" s="457"/>
+      <c r="K2" s="457"/>
+      <c r="L2" s="457"/>
+      <c r="M2" s="457"/>
+      <c r="N2" s="457"/>
+      <c r="O2" s="457"/>
+      <c r="P2" s="457"/>
+      <c r="Q2" s="457"/>
+      <c r="R2" s="457"/>
+      <c r="S2" s="457"/>
+      <c r="T2" s="457"/>
     </row>
     <row r="3" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -19947,120 +22663,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EC9312-1D6A-C146-B06E-16E6A54035B4}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="22.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="101" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="101" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B2" s="95">
-        <f>Master!$C$20</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="95">
-        <f>Master!$C$20</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="95">
-        <f>Master!$C$20</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="95">
-        <f>Master!$C$20</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="95">
-        <f>Master!$C$20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B3" s="95">
-        <v>10.857008</v>
-      </c>
-      <c r="C3" s="95">
-        <v>10.857008</v>
-      </c>
-      <c r="D3" s="95">
-        <v>10.857008</v>
-      </c>
-      <c r="E3" s="95">
-        <v>10.857008</v>
-      </c>
-      <c r="F3" s="95">
-        <v>10.857008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B4" s="95">
-        <v>2.2231700000000001</v>
-      </c>
-      <c r="C4" s="95">
-        <v>2.2231700000000001</v>
-      </c>
-      <c r="D4" s="95">
-        <v>2.2231700000000001</v>
-      </c>
-      <c r="E4" s="95">
-        <v>2.2231700000000001</v>
-      </c>
-      <c r="F4" s="95">
-        <v>2.2231700000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>484</v>
-      </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BF02C3-B992-44C7-A79C-D1E41573911A}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -20713,6 +23318,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BF7D8F-86F3-47E9-AB85-EE9B4CAB70E4}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -20740,16 +23346,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="405" t="str">
+      <c r="A1" s="406" t="str">
         <f>'ReadMe-Directions'!A1</f>
         <v>Immersive Model for Lake Mead based on the Principle of Divide Reservoir Inflow</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
+      <c r="B1" s="406"/>
+      <c r="C1" s="406"/>
+      <c r="D1" s="406"/>
+      <c r="E1" s="406"/>
+      <c r="F1" s="406"/>
+      <c r="G1" s="406"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -20758,15 +23364,15 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="413" t="s">
+      <c r="A3" s="414" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="413"/>
-      <c r="C3" s="413"/>
-      <c r="D3" s="413"/>
-      <c r="E3" s="413"/>
-      <c r="F3" s="413"/>
-      <c r="G3" s="413"/>
+      <c r="B3" s="414"/>
+      <c r="C3" s="414"/>
+      <c r="D3" s="414"/>
+      <c r="E3" s="414"/>
+      <c r="F3" s="414"/>
+      <c r="G3" s="414"/>
       <c r="H3" s="82"/>
       <c r="I3" s="82"/>
       <c r="J3" s="82"/>
@@ -20782,13 +23388,13 @@
       <c r="B4" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="415" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="415"/>
-      <c r="E4" s="415"/>
-      <c r="F4" s="415"/>
-      <c r="G4" s="416"/>
+      <c r="D4" s="416"/>
+      <c r="E4" s="416"/>
+      <c r="F4" s="416"/>
+      <c r="G4" s="417"/>
       <c r="N4" s="138" t="s">
         <v>329</v>
       </c>
@@ -20798,11 +23404,11 @@
         <v>238</v>
       </c>
       <c r="B5" s="111"/>
-      <c r="C5" s="417"/>
-      <c r="D5" s="412"/>
-      <c r="E5" s="412"/>
-      <c r="F5" s="412"/>
-      <c r="G5" s="412"/>
+      <c r="C5" s="418"/>
+      <c r="D5" s="413"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="413"/>
       <c r="N5" s="138"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -20810,11 +23416,11 @@
         <v>202</v>
       </c>
       <c r="B6" s="111"/>
-      <c r="C6" s="417"/>
-      <c r="D6" s="412"/>
-      <c r="E6" s="412"/>
-      <c r="F6" s="412"/>
-      <c r="G6" s="412"/>
+      <c r="C6" s="418"/>
+      <c r="D6" s="413"/>
+      <c r="E6" s="413"/>
+      <c r="F6" s="413"/>
+      <c r="G6" s="413"/>
       <c r="N6" s="139"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20822,11 +23428,11 @@
         <v>203</v>
       </c>
       <c r="B7" s="111"/>
-      <c r="C7" s="417"/>
-      <c r="D7" s="412"/>
-      <c r="E7" s="412"/>
-      <c r="F7" s="412"/>
-      <c r="G7" s="412"/>
+      <c r="C7" s="418"/>
+      <c r="D7" s="413"/>
+      <c r="E7" s="413"/>
+      <c r="F7" s="413"/>
+      <c r="G7" s="413"/>
       <c r="N7" s="139"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20834,11 +23440,11 @@
         <v>204</v>
       </c>
       <c r="B8" s="88"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
+      <c r="C8" s="413"/>
+      <c r="D8" s="413"/>
+      <c r="E8" s="413"/>
+      <c r="F8" s="413"/>
+      <c r="G8" s="413"/>
       <c r="N8" s="139"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20846,11 +23452,11 @@
         <v>18</v>
       </c>
       <c r="B9" s="88"/>
-      <c r="C9" s="418"/>
-      <c r="D9" s="418"/>
-      <c r="E9" s="418"/>
-      <c r="F9" s="418"/>
-      <c r="G9" s="418"/>
+      <c r="C9" s="419"/>
+      <c r="D9" s="419"/>
+      <c r="E9" s="419"/>
+      <c r="F9" s="419"/>
+      <c r="G9" s="419"/>
       <c r="N9" s="139"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20858,11 +23464,11 @@
         <v>277</v>
       </c>
       <c r="B10" s="88"/>
-      <c r="C10" s="412"/>
-      <c r="D10" s="412"/>
-      <c r="E10" s="412"/>
-      <c r="F10" s="412"/>
-      <c r="G10" s="412"/>
+      <c r="C10" s="413"/>
+      <c r="D10" s="413"/>
+      <c r="E10" s="413"/>
+      <c r="F10" s="413"/>
+      <c r="G10" s="413"/>
       <c r="N10" s="139"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20875,36 +23481,36 @@
       <c r="A12" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="419" t="s">
+      <c r="B12" s="420" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="420"/>
-      <c r="D12" s="421"/>
+      <c r="C12" s="421"/>
+      <c r="D12" s="422"/>
       <c r="N12" s="138" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="422" t="s">
+      <c r="B13" s="423" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="423"/>
-      <c r="D13" s="424"/>
+      <c r="C13" s="424"/>
+      <c r="D13" s="425"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="406" t="s">
+      <c r="B14" s="407" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="407"/>
-      <c r="D14" s="408"/>
+      <c r="C14" s="408"/>
+      <c r="D14" s="409"/>
       <c r="N14" s="139"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="409" t="s">
+      <c r="B15" s="410" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="410"/>
-      <c r="D15" s="411"/>
+      <c r="C15" s="411"/>
+      <c r="D15" s="412"/>
       <c r="N15" s="139"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -25726,184 +28332,164 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
   </mergeCells>
-  <conditionalFormatting sqref="C82">
-    <cfRule type="cellIs" dxfId="39" priority="100" operator="greaterThan">
-      <formula>$C$81</formula>
+  <conditionalFormatting sqref="H72">
+    <cfRule type="cellIs" dxfId="84" priority="219" operator="greaterThan">
+      <formula>$H$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H82">
+    <cfRule type="cellIs" dxfId="83" priority="202" operator="greaterThan">
+      <formula>$H$81</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H92">
+    <cfRule type="cellIs" dxfId="82" priority="192" operator="greaterThan">
+      <formula>$H$91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H112">
+    <cfRule type="cellIs" dxfId="81" priority="181" operator="greaterThan">
+      <formula>$H$111</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H122">
+    <cfRule type="cellIs" dxfId="80" priority="171" operator="greaterThan">
+      <formula>$H$121</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H102:L102">
+    <cfRule type="cellIs" dxfId="79" priority="187" operator="greaterThan">
+      <formula>$C$101</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I72">
+    <cfRule type="cellIs" dxfId="78" priority="218" operator="greaterThan">
+      <formula>$I$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I82">
+    <cfRule type="cellIs" dxfId="77" priority="201" operator="greaterThan">
+      <formula>$I$81</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I92">
+    <cfRule type="cellIs" dxfId="76" priority="191" operator="greaterThan">
+      <formula>$I$91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I112">
+    <cfRule type="cellIs" dxfId="75" priority="180" operator="greaterThan">
+      <formula>$I$111</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I122">
+    <cfRule type="cellIs" dxfId="74" priority="170" operator="greaterThan">
+      <formula>$I$121</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J72">
+    <cfRule type="cellIs" dxfId="73" priority="217" operator="greaterThan">
+      <formula>$J$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J82">
+    <cfRule type="cellIs" dxfId="72" priority="200" operator="greaterThan">
+      <formula>$J$81</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J92">
+    <cfRule type="cellIs" dxfId="71" priority="190" operator="greaterThan">
+      <formula>$J$91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J112">
+    <cfRule type="cellIs" dxfId="70" priority="179" operator="greaterThan">
+      <formula>$J$111</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J122">
+    <cfRule type="cellIs" dxfId="69" priority="169" operator="greaterThan">
+      <formula>$J$121</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K72">
+    <cfRule type="cellIs" dxfId="68" priority="216" operator="greaterThan">
+      <formula>$K$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K82">
+    <cfRule type="cellIs" dxfId="67" priority="199" operator="greaterThan">
+      <formula>$K$81</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K92">
+    <cfRule type="cellIs" dxfId="66" priority="189" operator="greaterThan">
+      <formula>$K$91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K112">
+    <cfRule type="cellIs" dxfId="65" priority="178" operator="greaterThan">
+      <formula>$K$111</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K122">
+    <cfRule type="cellIs" dxfId="64" priority="168" operator="greaterThan">
+      <formula>$K$121</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L72">
+    <cfRule type="cellIs" dxfId="63" priority="215" operator="greaterThan">
+      <formula>$L$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L82">
+    <cfRule type="cellIs" dxfId="62" priority="198" operator="greaterThan">
+      <formula>$L$81</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L92">
+    <cfRule type="cellIs" dxfId="61" priority="188" operator="greaterThan">
+      <formula>$L$91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L112">
+    <cfRule type="cellIs" dxfId="60" priority="177" operator="greaterThan">
+      <formula>$L$111</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L122">
+    <cfRule type="cellIs" dxfId="59" priority="167" operator="greaterThan">
+      <formula>$L$121</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72:G72">
-    <cfRule type="cellIs" dxfId="38" priority="41" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C82:G82">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
       <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92:G92">
-    <cfRule type="cellIs" dxfId="37" priority="90" operator="greaterThan">
-      <formula>$C$91</formula>
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="greaterThan">
+      <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:G102">
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="greaterThan">
-      <formula>$C$91</formula>
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
+      <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C112:G112">
-    <cfRule type="cellIs" dxfId="35" priority="4" operator="greaterThan">
-      <formula>$C$91</formula>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+      <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C122:G122">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="greaterThan">
-      <formula>$C$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D82">
-    <cfRule type="cellIs" dxfId="33" priority="31" operator="greaterThan">
-      <formula>$D$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E82">
-    <cfRule type="cellIs" dxfId="32" priority="22" operator="greaterThan">
-      <formula>$E$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="cellIs" dxfId="31" priority="18" operator="greaterThan">
-      <formula>$F$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G82">
-    <cfRule type="cellIs" dxfId="30" priority="12" operator="greaterThan">
-      <formula>$G$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H72">
-    <cfRule type="cellIs" dxfId="29" priority="187" operator="greaterThan">
-      <formula>$H$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H82">
-    <cfRule type="cellIs" dxfId="28" priority="170" operator="greaterThan">
-      <formula>$H$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H92">
-    <cfRule type="cellIs" dxfId="27" priority="160" operator="greaterThan">
-      <formula>$H$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H112">
-    <cfRule type="cellIs" dxfId="26" priority="149" operator="greaterThan">
-      <formula>$H$111</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H122">
-    <cfRule type="cellIs" dxfId="25" priority="139" operator="greaterThan">
-      <formula>$H$121</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H102:L102">
-    <cfRule type="cellIs" dxfId="24" priority="155" operator="greaterThan">
-      <formula>$C$101</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I72">
-    <cfRule type="cellIs" dxfId="23" priority="186" operator="greaterThan">
-      <formula>$I$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I82">
-    <cfRule type="cellIs" dxfId="22" priority="169" operator="greaterThan">
-      <formula>$I$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I92">
-    <cfRule type="cellIs" dxfId="21" priority="159" operator="greaterThan">
-      <formula>$I$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I112">
-    <cfRule type="cellIs" dxfId="20" priority="148" operator="greaterThan">
-      <formula>$I$111</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I122">
-    <cfRule type="cellIs" dxfId="19" priority="138" operator="greaterThan">
-      <formula>$I$121</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J72">
-    <cfRule type="cellIs" dxfId="18" priority="185" operator="greaterThan">
-      <formula>$J$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J82">
-    <cfRule type="cellIs" dxfId="17" priority="168" operator="greaterThan">
-      <formula>$J$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J92">
-    <cfRule type="cellIs" dxfId="16" priority="158" operator="greaterThan">
-      <formula>$J$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J112">
-    <cfRule type="cellIs" dxfId="15" priority="147" operator="greaterThan">
-      <formula>$J$111</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J122">
-    <cfRule type="cellIs" dxfId="14" priority="137" operator="greaterThan">
-      <formula>$J$121</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K72">
-    <cfRule type="cellIs" dxfId="13" priority="184" operator="greaterThan">
-      <formula>$K$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K82">
-    <cfRule type="cellIs" dxfId="12" priority="167" operator="greaterThan">
-      <formula>$K$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K92">
-    <cfRule type="cellIs" dxfId="11" priority="157" operator="greaterThan">
-      <formula>$K$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K112">
-    <cfRule type="cellIs" dxfId="10" priority="146" operator="greaterThan">
-      <formula>$K$111</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K122">
-    <cfRule type="cellIs" dxfId="9" priority="136" operator="greaterThan">
-      <formula>$K$121</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L72">
-    <cfRule type="cellIs" dxfId="8" priority="183" operator="greaterThan">
-      <formula>$L$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L82">
-    <cfRule type="cellIs" dxfId="7" priority="166" operator="greaterThan">
-      <formula>$L$81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L92">
-    <cfRule type="cellIs" dxfId="6" priority="156" operator="greaterThan">
-      <formula>$L$91</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L112">
-    <cfRule type="cellIs" dxfId="5" priority="145" operator="greaterThan">
-      <formula>$L$111</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L122">
-    <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThan">
-      <formula>$L$121</formula>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -25984,26 +28570,102 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="99" id="{40EBAACB-EEF6-AE4C-B1C4-B33647A64EA7}">
+          <x14:cfRule type="iconSet" priority="211" id="{0B4D75C4-D25A-44EA-B63E-E03692154A69}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$81</xm:f>
+                <xm:f>"h60"</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$81</xm:f>
+                <xm:f>"h60"</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="NoIcons" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>C82</xm:sqref>
+          <xm:sqref>H72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="40" id="{67BD5567-B9E3-294F-8090-EF2E01062FB6}">
+          <x14:cfRule type="iconSet" priority="210" id="{D9A4611E-EAFB-4D72-8EA7-BB20C2AA53D0}">
+            <x14:iconSet iconSet="3Symbols" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"i60"</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"i60"</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="209" id="{FC9241E0-399F-4612-9178-0FDDFFF0E42A}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$J$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$J$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="208" id="{DD71F70E-9732-4C09-96AD-AC28A6D96762}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$K$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$K$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>K72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="166" id="{C970D36A-412D-482A-B900-0C93FEFDE178}">
+            <x14:iconSet iconSet="3Symbols" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$L$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$L$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="11" id="{536B711C-2A93-3745-B644-9671CF4BB432}">
             <x14:iconSet iconSet="3Symbols2" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -26022,16 +28684,35 @@
           <xm:sqref>C72:G72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="89" id="{99C3FE96-8001-7B4F-9CCB-D74A3EE27990}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
+          <x14:cfRule type="iconSet" priority="9" id="{513362F3-E5E7-8A45-B64B-46B477B3204A}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>C82:G82</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="7" id="{48E41CD5-3F22-5341-9931-3B40B71195B0}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$C$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="NoIcons" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
@@ -26041,16 +28722,16 @@
           <xm:sqref>C92:G92</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{8BE61F95-23AB-D447-B42B-9156C2AB6BFE}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
+          <x14:cfRule type="iconSet" priority="5" id="{59438CAC-D4AD-F845-9441-FBF9F58BA5EC}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="NoIcons" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
@@ -26060,16 +28741,16 @@
           <xm:sqref>C102:G102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{91CD582D-6867-114D-97A4-814342EFE144}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
+          <x14:cfRule type="iconSet" priority="3" id="{34861A98-71F2-2E41-86AB-A28BE680D72F}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="NoIcons" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
@@ -26079,16 +28760,16 @@
           <xm:sqref>C112:G112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{1DB5C01C-A394-BF43-A8D0-172701BB16FE}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
+          <x14:cfRule type="iconSet" priority="1" id="{6C865FCD-C82C-DC45-8DCA-C1235A88B115}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>$C$91</xm:f>
+                <xm:f>$C$70</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="NoIcons" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
@@ -26096,177 +28777,6 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>C122:G122</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="51" id="{91D44B4A-8C25-1746-8718-8544A152DE08}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>$D$81</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$D$81</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{8B0BB9B0-09E7-A840-9D64-16D722ED25F9}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$E$81</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$E$81</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{DD5AD040-6C8D-C449-9BAE-399A2BD193AF}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$F$81</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$F$81</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{96D22E39-A667-E445-9146-BFF7CB43E1E0}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$G$81</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$G$81</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="179" id="{0B4D75C4-D25A-44EA-B63E-E03692154A69}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"h60"</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"h60"</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="178" id="{D9A4611E-EAFB-4D72-8EA7-BB20C2AA53D0}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"i60"</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"i60"</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="177" id="{FC9241E0-399F-4612-9178-0FDDFFF0E42A}">
-            <x14:iconSet iconSet="3Symbols2" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$J$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$J$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>J72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="176" id="{DD71F70E-9732-4C09-96AD-AC28A6D96762}">
-            <x14:iconSet iconSet="3Symbols2" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$K$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$K$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>K72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="134" id="{C970D36A-412D-482A-B900-0C93FEFDE178}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$L$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$L$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -26276,6 +28786,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA15763-059F-401A-BB99-8A737E404CC4}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:BF51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -26346,62 +28857,62 @@
       <c r="G5" s="185" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="438" t="s">
+      <c r="I5" s="439" t="s">
         <v>423</v>
       </c>
-      <c r="J5" s="439"/>
-      <c r="K5" s="439"/>
-      <c r="L5" s="439"/>
-      <c r="M5" s="439"/>
-      <c r="N5" s="439"/>
-      <c r="O5" s="439"/>
-      <c r="P5" s="439"/>
-      <c r="Q5" s="439"/>
-      <c r="R5" s="439"/>
-      <c r="S5" s="439"/>
-      <c r="T5" s="439"/>
-      <c r="U5" s="439"/>
-      <c r="V5" s="439"/>
-      <c r="W5" s="440"/>
+      <c r="J5" s="440"/>
+      <c r="K5" s="440"/>
+      <c r="L5" s="440"/>
+      <c r="M5" s="440"/>
+      <c r="N5" s="440"/>
+      <c r="O5" s="440"/>
+      <c r="P5" s="440"/>
+      <c r="Q5" s="440"/>
+      <c r="R5" s="440"/>
+      <c r="S5" s="440"/>
+      <c r="T5" s="440"/>
+      <c r="U5" s="440"/>
+      <c r="V5" s="440"/>
+      <c r="W5" s="441"/>
       <c r="Y5" s="192"/>
       <c r="Z5" s="192"/>
       <c r="AA5" s="192"/>
       <c r="AB5" s="334"/>
     </row>
     <row r="6" spans="1:53" s="184" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="427" t="s">
+      <c r="B6" s="428" t="s">
         <v>228</v>
       </c>
-      <c r="C6" s="428"/>
-      <c r="D6" s="428"/>
-      <c r="E6" s="428"/>
-      <c r="F6" s="428"/>
-      <c r="G6" s="429"/>
-      <c r="I6" s="441" t="s">
+      <c r="C6" s="429"/>
+      <c r="D6" s="429"/>
+      <c r="E6" s="429"/>
+      <c r="F6" s="429"/>
+      <c r="G6" s="430"/>
+      <c r="I6" s="442" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="425" t="s">
+      <c r="J6" s="426" t="s">
         <v>409</v>
       </c>
-      <c r="K6" s="425" t="s">
+      <c r="K6" s="426" t="s">
         <v>408</v>
       </c>
-      <c r="L6" s="443" t="s">
+      <c r="L6" s="444" t="s">
         <v>215</v>
       </c>
-      <c r="M6" s="444"/>
-      <c r="N6" s="444"/>
-      <c r="O6" s="444"/>
-      <c r="P6" s="444"/>
-      <c r="Q6" s="445"/>
-      <c r="R6" s="430" t="s">
+      <c r="M6" s="445"/>
+      <c r="N6" s="445"/>
+      <c r="O6" s="445"/>
+      <c r="P6" s="445"/>
+      <c r="Q6" s="446"/>
+      <c r="R6" s="431" t="s">
         <v>216</v>
       </c>
-      <c r="S6" s="431"/>
-      <c r="T6" s="431"/>
-      <c r="U6" s="431"/>
-      <c r="V6" s="431"/>
-      <c r="W6" s="432"/>
+      <c r="S6" s="432"/>
+      <c r="T6" s="432"/>
+      <c r="U6" s="432"/>
+      <c r="V6" s="432"/>
+      <c r="W6" s="433"/>
       <c r="Y6" s="307"/>
       <c r="Z6" s="307"/>
       <c r="AA6" s="307"/>
@@ -26427,9 +28938,9 @@
         <f>SUM(C7:F7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="442"/>
-      <c r="J7" s="442"/>
-      <c r="K7" s="442"/>
+      <c r="I7" s="443"/>
+      <c r="J7" s="443"/>
+      <c r="K7" s="443"/>
       <c r="L7" s="186" t="s">
         <v>410</v>
       </c>
@@ -26633,14 +29144,14 @@
       <c r="AZ9" s="285"/>
     </row>
     <row r="10" spans="1:53" s="192" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="B10" s="433" t="s">
+      <c r="B10" s="434" t="s">
         <v>237</v>
       </c>
-      <c r="C10" s="433"/>
-      <c r="D10" s="433"/>
-      <c r="E10" s="433"/>
-      <c r="F10" s="433"/>
-      <c r="G10" s="433"/>
+      <c r="C10" s="434"/>
+      <c r="D10" s="434"/>
+      <c r="E10" s="434"/>
+      <c r="F10" s="434"/>
+      <c r="G10" s="434"/>
       <c r="I10" s="244" t="s">
         <v>231</v>
       </c>
@@ -27124,13 +29635,13 @@
       <c r="B16" s="193" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="434" t="s">
+      <c r="C16" s="435" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="435"/>
-      <c r="E16" s="435"/>
-      <c r="F16" s="435"/>
-      <c r="G16" s="436"/>
+      <c r="D16" s="436"/>
+      <c r="E16" s="436"/>
+      <c r="F16" s="436"/>
+      <c r="G16" s="437"/>
       <c r="I16" s="244" t="s">
         <v>404</v>
       </c>
@@ -27246,59 +29757,59 @@
     </row>
     <row r="18" spans="2:58" s="192" customFormat="1" ht="14" x14ac:dyDescent="0.15"/>
     <row r="19" spans="2:58" s="192" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I19" s="437" t="s">
+      <c r="I19" s="438" t="s">
         <v>424</v>
       </c>
-      <c r="J19" s="437"/>
-      <c r="K19" s="437"/>
-      <c r="L19" s="437"/>
-      <c r="M19" s="437"/>
-      <c r="N19" s="437"/>
-      <c r="O19" s="437"/>
-      <c r="P19" s="437"/>
-      <c r="Q19" s="437"/>
-      <c r="R19" s="437"/>
-      <c r="S19" s="437"/>
-      <c r="T19" s="437"/>
-      <c r="U19" s="437"/>
+      <c r="J19" s="438"/>
+      <c r="K19" s="438"/>
+      <c r="L19" s="438"/>
+      <c r="M19" s="438"/>
+      <c r="N19" s="438"/>
+      <c r="O19" s="438"/>
+      <c r="P19" s="438"/>
+      <c r="Q19" s="438"/>
+      <c r="R19" s="438"/>
+      <c r="S19" s="438"/>
+      <c r="T19" s="438"/>
+      <c r="U19" s="438"/>
       <c r="Z19" s="250"/>
       <c r="AA19" s="250"/>
       <c r="AB19" s="250"/>
       <c r="AC19" s="250"/>
     </row>
     <row r="20" spans="2:58" s="192" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I20" s="425" t="s">
+      <c r="I20" s="426" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="425" t="s">
+      <c r="J20" s="426" t="s">
         <v>213</v>
       </c>
-      <c r="K20" s="425" t="s">
+      <c r="K20" s="426" t="s">
         <v>214</v>
       </c>
-      <c r="L20" s="427" t="s">
+      <c r="L20" s="428" t="s">
         <v>215</v>
       </c>
-      <c r="M20" s="428"/>
-      <c r="N20" s="428"/>
-      <c r="O20" s="428"/>
-      <c r="P20" s="429"/>
-      <c r="Q20" s="430" t="s">
+      <c r="M20" s="429"/>
+      <c r="N20" s="429"/>
+      <c r="O20" s="429"/>
+      <c r="P20" s="430"/>
+      <c r="Q20" s="431" t="s">
         <v>216</v>
       </c>
-      <c r="R20" s="431"/>
-      <c r="S20" s="431"/>
-      <c r="T20" s="431"/>
-      <c r="U20" s="432"/>
+      <c r="R20" s="432"/>
+      <c r="S20" s="432"/>
+      <c r="T20" s="432"/>
+      <c r="U20" s="433"/>
       <c r="Z20" s="254"/>
       <c r="AA20" s="254"/>
       <c r="AB20" s="254"/>
       <c r="AC20" s="254"/>
     </row>
     <row r="21" spans="2:58" s="192" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I21" s="426"/>
-      <c r="J21" s="426"/>
-      <c r="K21" s="426"/>
+      <c r="I21" s="427"/>
+      <c r="J21" s="427"/>
+      <c r="K21" s="427"/>
       <c r="L21" s="186" t="s">
         <v>218</v>
       </c>
@@ -28342,6 +30853,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876BA06C-E963-43DD-B933-307F043834EF}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -28640,6 +31152,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC23DDF-F435-4D30-95DE-B930467A5C28}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -28667,16 +31180,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="447" t="e">
+      <c r="A1" s="448" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="447"/>
-      <c r="C1" s="447"/>
-      <c r="D1" s="447"/>
-      <c r="E1" s="447"/>
-      <c r="F1" s="447"/>
-      <c r="G1" s="447"/>
+      <c r="B1" s="448"/>
+      <c r="C1" s="448"/>
+      <c r="D1" s="448"/>
+      <c r="E1" s="448"/>
+      <c r="F1" s="448"/>
+      <c r="G1" s="448"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -28685,15 +31198,15 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="413" t="s">
+      <c r="A3" s="414" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="413"/>
-      <c r="C3" s="413"/>
-      <c r="D3" s="413"/>
-      <c r="E3" s="413"/>
-      <c r="F3" s="413"/>
-      <c r="G3" s="413"/>
+      <c r="B3" s="414"/>
+      <c r="C3" s="414"/>
+      <c r="D3" s="414"/>
+      <c r="E3" s="414"/>
+      <c r="F3" s="414"/>
+      <c r="G3" s="414"/>
       <c r="H3" s="82"/>
       <c r="I3" s="82"/>
       <c r="J3" s="82"/>
@@ -28709,13 +31222,13 @@
       <c r="B4" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="415" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="415"/>
-      <c r="E4" s="415"/>
-      <c r="F4" s="415"/>
-      <c r="G4" s="416"/>
+      <c r="D4" s="416"/>
+      <c r="E4" s="416"/>
+      <c r="F4" s="416"/>
+      <c r="G4" s="417"/>
       <c r="N4" s="136" t="s">
         <v>128</v>
       </c>
@@ -28725,11 +31238,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="111"/>
-      <c r="C5" s="417"/>
-      <c r="D5" s="412"/>
-      <c r="E5" s="412"/>
-      <c r="F5" s="412"/>
-      <c r="G5" s="412"/>
+      <c r="C5" s="418"/>
+      <c r="D5" s="413"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="413"/>
       <c r="N5" s="139"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -28737,11 +31250,11 @@
         <v>17</v>
       </c>
       <c r="B6" s="111"/>
-      <c r="C6" s="417"/>
-      <c r="D6" s="412"/>
-      <c r="E6" s="412"/>
-      <c r="F6" s="412"/>
-      <c r="G6" s="412"/>
+      <c r="C6" s="418"/>
+      <c r="D6" s="413"/>
+      <c r="E6" s="413"/>
+      <c r="F6" s="413"/>
+      <c r="G6" s="413"/>
       <c r="N6" s="139"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -28749,11 +31262,11 @@
         <v>18</v>
       </c>
       <c r="B7" s="111"/>
-      <c r="C7" s="417"/>
-      <c r="D7" s="412"/>
-      <c r="E7" s="412"/>
-      <c r="F7" s="412"/>
-      <c r="G7" s="412"/>
+      <c r="C7" s="418"/>
+      <c r="D7" s="413"/>
+      <c r="E7" s="413"/>
+      <c r="F7" s="413"/>
+      <c r="G7" s="413"/>
       <c r="N7" s="139"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -28761,11 +31274,11 @@
         <v>39</v>
       </c>
       <c r="B8" s="88"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
+      <c r="C8" s="413"/>
+      <c r="D8" s="413"/>
+      <c r="E8" s="413"/>
+      <c r="F8" s="413"/>
+      <c r="G8" s="413"/>
       <c r="N8" s="139"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -28773,11 +31286,11 @@
         <v>162</v>
       </c>
       <c r="B9" s="88"/>
-      <c r="C9" s="418"/>
-      <c r="D9" s="418"/>
-      <c r="E9" s="418"/>
-      <c r="F9" s="418"/>
-      <c r="G9" s="418"/>
+      <c r="C9" s="419"/>
+      <c r="D9" s="419"/>
+      <c r="E9" s="419"/>
+      <c r="F9" s="419"/>
+      <c r="G9" s="419"/>
       <c r="N9" s="139"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -28785,11 +31298,11 @@
         <v>40</v>
       </c>
       <c r="B10" s="112"/>
-      <c r="C10" s="446"/>
-      <c r="D10" s="446"/>
-      <c r="E10" s="446"/>
-      <c r="F10" s="446"/>
-      <c r="G10" s="446"/>
+      <c r="C10" s="447"/>
+      <c r="D10" s="447"/>
+      <c r="E10" s="447"/>
+      <c r="F10" s="447"/>
+      <c r="G10" s="447"/>
       <c r="N10" s="139"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -28802,37 +31315,37 @@
       <c r="A12" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="419" t="s">
+      <c r="B12" s="420" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="420"/>
-      <c r="D12" s="421"/>
+      <c r="C12" s="421"/>
+      <c r="D12" s="422"/>
       <c r="N12" s="138" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="422" t="s">
+      <c r="B13" s="423" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="423"/>
-      <c r="D13" s="424"/>
+      <c r="C13" s="424"/>
+      <c r="D13" s="425"/>
       <c r="N13" s="139"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="406" t="s">
+      <c r="B14" s="407" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="407"/>
-      <c r="D14" s="408"/>
+      <c r="C14" s="408"/>
+      <c r="D14" s="409"/>
       <c r="N14" s="139"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="409" t="s">
+      <c r="B15" s="410" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="410"/>
-      <c r="D15" s="411"/>
+      <c r="C15" s="411"/>
+      <c r="D15" s="412"/>
       <c r="N15" s="139"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -30093,6 +32606,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA1955-E131-4760-B8B7-F63C70A9C255}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -30119,26 +32633,26 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="448" t="s">
+      <c r="D3" s="449" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="448"/>
-      <c r="F3" s="448" t="s">
+      <c r="E3" s="449"/>
+      <c r="F3" s="449" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="448"/>
-      <c r="H3" s="448"/>
-      <c r="I3" s="448" t="s">
+      <c r="G3" s="449"/>
+      <c r="H3" s="449"/>
+      <c r="I3" s="449" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="448"/>
-      <c r="K3" s="448"/>
+      <c r="J3" s="449"/>
+      <c r="K3" s="449"/>
       <c r="L3" s="131"/>
-      <c r="M3" s="448" t="s">
+      <c r="M3" s="449" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="448"/>
-      <c r="O3" s="448"/>
+      <c r="N3" s="449"/>
+      <c r="O3" s="449"/>
     </row>
     <row r="4" spans="1:16" s="45" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
@@ -31196,6 +33710,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5020C709-D0B6-42F6-9872-67AE3BF5320E}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -31435,16 +33950,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>$B$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>$B$8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>$B$9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>$B$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31455,6 +33970,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A14D89E-14EF-4823-8B43-9AC037BFB8AB}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M689"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>

--- a/LakeMeadWaterBankDivideInflow.xlsx
+++ b/LakeMeadWaterBankDivideInflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anabelle/Documents/LakeMeadDivideInflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E388BF-DB80-2343-A335-83E2005A8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA9146B-B985-1A49-903B-4C59A3160FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17120" yWindow="-24000" windowWidth="38400" windowHeight="24000" activeTab="2" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" firstSheet="1" activeTab="3" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe-Directions" sheetId="62" r:id="rId1"/>
@@ -3332,7 +3332,7 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="461">
+  <cellXfs count="460">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4265,74 +4265,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="2" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4388,6 +4322,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4426,6 +4366,69 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="27" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="2" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4487,12 +4490,6 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4501,15 +4498,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4541,6 +4529,9 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4550,11 +4541,23 @@
     <xf numFmtId="0" fontId="18" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4577,18 +4580,14 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -4607,157 +4606,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="95">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <font>
         <color auto="1"/>
@@ -4795,446 +4644,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5642,7 +5051,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D24E5FC-1654-6947-839F-964DB2CA094A}" type="CELLRANGE">
+                    <a:fld id="{EBF23E2E-2F5E-FB42-AB63-DB931375975D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5661,7 +5070,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5676,7 +5084,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{72934C22-0618-9F4B-8AE7-B79C7868C9B0}" type="CELLRANGE">
+                    <a:fld id="{8A0C4FBB-5355-F74D-8D2D-2DA38038DF79}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5710,7 +5118,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C21D1A2C-6282-9743-A7F1-5F1B558BE6B0}" type="CELLRANGE">
+                    <a:fld id="{66CE1E64-6E6C-A741-B9FF-B1A3E14E1789}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5744,7 +5152,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{14A3BFD1-22BA-674D-AF1C-FADC2ABD3D23}" type="CELLRANGE">
+                    <a:fld id="{EF0F5A83-36EC-DD46-B776-7BA8596A5862}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5778,7 +5186,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0E1BBA5-915F-C048-A98C-C9A536F16FDB}" type="CELLRANGE">
+                    <a:fld id="{DC116C19-4A6D-AA4C-B54B-A647C8D03CA9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5934,7 +5342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{525EF4FE-6C61-214E-A54E-4D55904B160B}" type="CELLRANGE">
+                    <a:fld id="{9F8CB4F4-6ECE-BD4A-A6CF-972CCFFC0562}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5953,7 +5361,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5968,7 +5375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A4B2256-B98F-ED41-9D96-6150B3EBD74B}" type="CELLRANGE">
+                    <a:fld id="{31CA6072-10E9-3C46-AD06-97316F64A592}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6002,7 +5409,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3274F16B-47DA-8A47-B58B-1F92A236A5FE}" type="CELLRANGE">
+                    <a:fld id="{A2E39BFE-8B1A-4745-B200-94F346C83CED}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6036,7 +5443,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45DF277B-9831-AB4A-AFFA-A8EC895531FD}" type="CELLRANGE">
+                    <a:fld id="{2499BB8C-F587-4146-BB34-6DFF93EFC078}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6070,7 +5477,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C67022F-7788-AE40-8DB3-B6AC4217E0DB}" type="CELLRANGE">
+                    <a:fld id="{A0CAC97C-DF1B-C04B-B61D-C49F5543031C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6203,7 +5610,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{158A015D-D354-2E4D-A4EB-502E0C84880B}" type="CELLRANGE">
+                    <a:fld id="{49AE8E98-D96E-C74A-A99E-99AFC189000D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6222,7 +5629,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -6237,7 +5643,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C02BD27C-BC4F-C34E-88D4-40F3FDFBA8EA}" type="CELLRANGE">
+                    <a:fld id="{E54DE757-4BBD-8146-BDD1-459DE9235F07}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6271,7 +5677,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6F26EA52-4B94-3E4F-B0FC-8E5CA7786468}" type="CELLRANGE">
+                    <a:fld id="{6A9916F2-E79C-3C45-B378-EFB0C341D866}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6305,7 +5711,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA0DDC15-479E-1947-BCDB-E77E7C2D5781}" type="CELLRANGE">
+                    <a:fld id="{EF8C5855-4A3D-AD48-BCE2-1004A84A0B77}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6339,7 +5745,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EBEB41C6-0067-7740-97BF-32048C9DC0C4}" type="CELLRANGE">
+                    <a:fld id="{A6ACAE26-E4F5-BB48-874C-D4A022864063}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6472,7 +5878,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DAA6EC7F-54E3-8043-9D21-3B2E3F400D74}" type="CELLRANGE">
+                    <a:fld id="{9AA38807-3F44-174F-AE74-16901B16D683}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6491,7 +5897,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -6506,7 +5911,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{744498B0-F271-FF46-97AE-1FDB7D557FF1}" type="CELLRANGE">
+                    <a:fld id="{AA692FE6-6F5B-F34C-B0B7-25516FD9289C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6540,7 +5945,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8A509EC7-2C02-2740-A8B3-0482D2A58E7D}" type="CELLRANGE">
+                    <a:fld id="{9D0F4FE8-8FB3-DE4D-A163-B8FBEEA93F87}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6574,7 +5979,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A15D912-EC3E-0748-9FA3-091A7949E1BB}" type="CELLRANGE">
+                    <a:fld id="{F2AB8AB9-16A2-8147-B77F-158196B08B7C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6608,7 +6013,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C6CB93D-783C-8240-9677-AE783C99D599}" type="CELLRANGE">
+                    <a:fld id="{A83C57D0-9F1A-F34F-87F2-0CA72509BA10}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6764,7 +6169,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{89EC99EE-31B2-2648-B269-B2F9E13BE846}" type="CELLRANGE">
+                    <a:fld id="{81E1F7EE-DB72-B744-BFEE-FCDC577E285A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6783,7 +6188,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -6798,7 +6202,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{070111C5-EDF9-D34F-9552-8CD0A7A9C22F}" type="CELLRANGE">
+                    <a:fld id="{5113DD99-3FF1-E547-AA39-EE50B5AAF7E6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6832,7 +6236,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27744255-E334-294B-A8E2-DB08D4FA7D47}" type="CELLRANGE">
+                    <a:fld id="{F99E226C-D08B-D447-8FF9-F10EC8FE6F2E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6866,7 +6270,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2E64831-4952-2F46-9D05-19383E57DDAC}" type="CELLRANGE">
+                    <a:fld id="{3EA03092-5907-A743-A0DA-EBBEB9478A2C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6900,7 +6304,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B381459-5668-5D4E-AB04-793C69287278}" type="CELLRANGE">
+                    <a:fld id="{C0310E57-564E-CF44-B4A8-C74C65553B22}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7059,7 +6463,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA4C0E14-7AF3-144F-B0CB-01238F726396}" type="CELLRANGE">
+                    <a:fld id="{A65EA91E-A9EB-EC42-9E43-419836E2AF26}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7078,7 +6482,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7093,7 +6496,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D64EC274-DCCC-8F41-B30E-FFC30047DC83}" type="CELLRANGE">
+                    <a:fld id="{D5451E50-1C5B-2C44-9A34-5533F3AECB67}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7127,7 +6530,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{32DAA80A-6151-424C-A4AB-911C496E573E}" type="CELLRANGE">
+                    <a:fld id="{9DD5FF91-74D7-3843-BCEB-9B2248D873DE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7161,7 +6564,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5E9ECFCB-58F2-B743-9A2F-FDED1119B5FC}" type="CELLRANGE">
+                    <a:fld id="{657CFC1C-66DF-674F-943A-7C46AD540C8A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7195,7 +6598,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6EB25BD2-3AF1-644B-8735-E39BD97FD70D}" type="CELLRANGE">
+                    <a:fld id="{51EF811A-1335-FA4C-AB3A-DBD27D3018B1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7503,10 +6906,6 @@
                   <a:prstGeom prst="rect">
                     <a:avLst/>
                   </a:prstGeom>
-                  <a:noFill/>
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
                 </c15:spPr>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
@@ -8123,26 +7522,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
@@ -17932,568 +17311,7 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -19268,7 +18086,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8681493" cy="6293134"/>
+    <xdr:ext cx="8669421" cy="6283158"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -19852,20 +18670,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="378" t="s">
+      <c r="A1" s="356" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="378"/>
-      <c r="I1" s="378"/>
-      <c r="J1" s="378"/>
-      <c r="K1" s="378"/>
-      <c r="L1" s="378"/>
+      <c r="B1" s="356"/>
+      <c r="C1" s="356"/>
+      <c r="D1" s="356"/>
+      <c r="E1" s="356"/>
+      <c r="F1" s="356"/>
+      <c r="G1" s="356"/>
+      <c r="H1" s="356"/>
+      <c r="I1" s="356"/>
+      <c r="J1" s="356"/>
+      <c r="K1" s="356"/>
+      <c r="L1" s="356"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -19891,41 +18709,41 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:18" s="52" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="379" t="s">
+      <c r="A4" s="357" t="s">
         <v>296</v>
       </c>
-      <c r="B4" s="380"/>
-      <c r="C4" s="380"/>
-      <c r="D4" s="380"/>
-      <c r="E4" s="380"/>
-      <c r="F4" s="380"/>
-      <c r="G4" s="380"/>
-      <c r="H4" s="380"/>
-      <c r="I4" s="380"/>
-      <c r="J4" s="380"/>
-      <c r="K4" s="380"/>
-      <c r="L4" s="381"/>
-      <c r="N4" s="382"/>
-      <c r="O4" s="382"/>
-      <c r="P4" s="382"/>
-      <c r="Q4" s="382"/>
-      <c r="R4" s="382"/>
+      <c r="B4" s="358"/>
+      <c r="C4" s="358"/>
+      <c r="D4" s="358"/>
+      <c r="E4" s="358"/>
+      <c r="F4" s="358"/>
+      <c r="G4" s="358"/>
+      <c r="H4" s="358"/>
+      <c r="I4" s="358"/>
+      <c r="J4" s="358"/>
+      <c r="K4" s="358"/>
+      <c r="L4" s="359"/>
+      <c r="N4" s="360"/>
+      <c r="O4" s="360"/>
+      <c r="P4" s="360"/>
+      <c r="Q4" s="360"/>
+      <c r="R4" s="360"/>
     </row>
     <row r="5" spans="1:18" s="52" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="361" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="384"/>
-      <c r="C5" s="384"/>
-      <c r="D5" s="384"/>
-      <c r="E5" s="384"/>
-      <c r="F5" s="384"/>
-      <c r="G5" s="384"/>
-      <c r="H5" s="384"/>
-      <c r="I5" s="384"/>
-      <c r="J5" s="384"/>
-      <c r="K5" s="384"/>
-      <c r="L5" s="385"/>
+      <c r="B5" s="362"/>
+      <c r="C5" s="362"/>
+      <c r="D5" s="362"/>
+      <c r="E5" s="362"/>
+      <c r="F5" s="362"/>
+      <c r="G5" s="362"/>
+      <c r="H5" s="362"/>
+      <c r="I5" s="362"/>
+      <c r="J5" s="362"/>
+      <c r="K5" s="362"/>
+      <c r="L5" s="363"/>
       <c r="N5" s="110"/>
       <c r="O5" s="110"/>
       <c r="P5" s="110"/>
@@ -19933,20 +18751,20 @@
       <c r="R5" s="110"/>
     </row>
     <row r="6" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="383" t="s">
+      <c r="A6" s="361" t="s">
         <v>297</v>
       </c>
-      <c r="B6" s="384"/>
-      <c r="C6" s="384"/>
-      <c r="D6" s="384"/>
-      <c r="E6" s="384"/>
-      <c r="F6" s="384"/>
-      <c r="G6" s="384"/>
-      <c r="H6" s="384"/>
-      <c r="I6" s="384"/>
-      <c r="J6" s="384"/>
-      <c r="K6" s="384"/>
-      <c r="L6" s="385"/>
+      <c r="B6" s="362"/>
+      <c r="C6" s="362"/>
+      <c r="D6" s="362"/>
+      <c r="E6" s="362"/>
+      <c r="F6" s="362"/>
+      <c r="G6" s="362"/>
+      <c r="H6" s="362"/>
+      <c r="I6" s="362"/>
+      <c r="J6" s="362"/>
+      <c r="K6" s="362"/>
+      <c r="L6" s="363"/>
       <c r="N6" s="110"/>
       <c r="O6" s="110"/>
       <c r="P6" s="110"/>
@@ -19955,19 +18773,19 @@
     </row>
     <row r="7" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="214"/>
-      <c r="B7" s="384" t="s">
+      <c r="B7" s="362" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="384"/>
-      <c r="D7" s="384"/>
-      <c r="E7" s="384"/>
-      <c r="F7" s="384"/>
-      <c r="G7" s="384"/>
-      <c r="H7" s="384"/>
-      <c r="I7" s="384"/>
-      <c r="J7" s="384"/>
-      <c r="K7" s="384"/>
-      <c r="L7" s="385"/>
+      <c r="C7" s="362"/>
+      <c r="D7" s="362"/>
+      <c r="E7" s="362"/>
+      <c r="F7" s="362"/>
+      <c r="G7" s="362"/>
+      <c r="H7" s="362"/>
+      <c r="I7" s="362"/>
+      <c r="J7" s="362"/>
+      <c r="K7" s="362"/>
+      <c r="L7" s="363"/>
       <c r="N7" s="110"/>
       <c r="O7" s="110"/>
       <c r="P7" s="110"/>
@@ -19976,19 +18794,19 @@
     </row>
     <row r="8" spans="1:18" s="52" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="215"/>
-      <c r="B8" s="399" t="s">
+      <c r="B8" s="379" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="399"/>
-      <c r="D8" s="399"/>
-      <c r="E8" s="399"/>
-      <c r="F8" s="399"/>
-      <c r="G8" s="399"/>
-      <c r="H8" s="399"/>
-      <c r="I8" s="399"/>
-      <c r="J8" s="399"/>
-      <c r="K8" s="399"/>
-      <c r="L8" s="400"/>
+      <c r="C8" s="379"/>
+      <c r="D8" s="379"/>
+      <c r="E8" s="379"/>
+      <c r="F8" s="379"/>
+      <c r="G8" s="379"/>
+      <c r="H8" s="379"/>
+      <c r="I8" s="379"/>
+      <c r="J8" s="379"/>
+      <c r="K8" s="379"/>
+      <c r="L8" s="380"/>
       <c r="N8" s="110"/>
       <c r="O8" s="110"/>
       <c r="P8" s="110"/>
@@ -20010,20 +18828,20 @@
       <c r="L9" s="110"/>
     </row>
     <row r="10" spans="1:18" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="401" t="s">
+      <c r="A10" s="381" t="s">
         <v>334</v>
       </c>
-      <c r="B10" s="402"/>
-      <c r="C10" s="402"/>
-      <c r="D10" s="402"/>
-      <c r="E10" s="402"/>
-      <c r="F10" s="402"/>
-      <c r="G10" s="402"/>
-      <c r="H10" s="402"/>
-      <c r="I10" s="402"/>
-      <c r="J10" s="402"/>
-      <c r="K10" s="402"/>
-      <c r="L10" s="403"/>
+      <c r="B10" s="382"/>
+      <c r="C10" s="382"/>
+      <c r="D10" s="382"/>
+      <c r="E10" s="382"/>
+      <c r="F10" s="382"/>
+      <c r="G10" s="382"/>
+      <c r="H10" s="382"/>
+      <c r="I10" s="382"/>
+      <c r="J10" s="382"/>
+      <c r="K10" s="382"/>
+      <c r="L10" s="383"/>
     </row>
     <row r="11" spans="1:18" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="344"/>
@@ -20043,19 +18861,19 @@
       <c r="A12" s="344" t="s">
         <v>335</v>
       </c>
-      <c r="B12" s="404" t="s">
+      <c r="B12" s="384" t="s">
         <v>478</v>
       </c>
-      <c r="C12" s="404"/>
-      <c r="D12" s="404"/>
-      <c r="E12" s="404"/>
-      <c r="F12" s="404"/>
-      <c r="G12" s="404"/>
-      <c r="H12" s="404"/>
-      <c r="I12" s="404"/>
-      <c r="J12" s="404"/>
-      <c r="K12" s="404"/>
-      <c r="L12" s="405"/>
+      <c r="C12" s="384"/>
+      <c r="D12" s="384"/>
+      <c r="E12" s="384"/>
+      <c r="F12" s="384"/>
+      <c r="G12" s="384"/>
+      <c r="H12" s="384"/>
+      <c r="I12" s="384"/>
+      <c r="J12" s="384"/>
+      <c r="K12" s="384"/>
+      <c r="L12" s="385"/>
     </row>
     <row r="13" spans="1:18" s="57" customFormat="1" ht="231" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="344"/>
@@ -20075,19 +18893,19 @@
       <c r="A14" s="235" t="s">
         <v>336</v>
       </c>
-      <c r="B14" s="354" t="s">
+      <c r="B14" s="403" t="s">
         <v>338</v>
       </c>
-      <c r="C14" s="354"/>
-      <c r="D14" s="354"/>
-      <c r="E14" s="354"/>
-      <c r="F14" s="354"/>
-      <c r="G14" s="354"/>
-      <c r="H14" s="354"/>
-      <c r="I14" s="354"/>
-      <c r="J14" s="354"/>
-      <c r="K14" s="354"/>
-      <c r="L14" s="355"/>
+      <c r="C14" s="403"/>
+      <c r="D14" s="403"/>
+      <c r="E14" s="403"/>
+      <c r="F14" s="403"/>
+      <c r="G14" s="403"/>
+      <c r="H14" s="403"/>
+      <c r="I14" s="403"/>
+      <c r="J14" s="403"/>
+      <c r="K14" s="403"/>
+      <c r="L14" s="404"/>
     </row>
     <row r="15" spans="1:18" s="57" customFormat="1" ht="161.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="227"/>
@@ -20107,51 +18925,51 @@
       <c r="A16" s="235" t="s">
         <v>337</v>
       </c>
-      <c r="B16" s="354" t="s">
+      <c r="B16" s="403" t="s">
         <v>339</v>
       </c>
-      <c r="C16" s="354"/>
-      <c r="D16" s="354"/>
-      <c r="E16" s="354"/>
-      <c r="F16" s="354"/>
-      <c r="G16" s="354"/>
-      <c r="H16" s="354"/>
-      <c r="I16" s="354"/>
-      <c r="J16" s="354"/>
-      <c r="K16" s="354"/>
-      <c r="L16" s="355"/>
+      <c r="C16" s="403"/>
+      <c r="D16" s="403"/>
+      <c r="E16" s="403"/>
+      <c r="F16" s="403"/>
+      <c r="G16" s="403"/>
+      <c r="H16" s="403"/>
+      <c r="I16" s="403"/>
+      <c r="J16" s="403"/>
+      <c r="K16" s="403"/>
+      <c r="L16" s="404"/>
     </row>
     <row r="17" spans="1:14" s="57" customFormat="1" ht="90.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="227"/>
-      <c r="B17" s="356"/>
-      <c r="C17" s="356"/>
-      <c r="D17" s="356"/>
-      <c r="E17" s="356"/>
-      <c r="F17" s="356"/>
-      <c r="G17" s="356"/>
-      <c r="H17" s="356"/>
-      <c r="I17" s="356"/>
-      <c r="J17" s="356"/>
-      <c r="K17" s="356"/>
-      <c r="L17" s="357"/>
+      <c r="B17" s="405"/>
+      <c r="C17" s="405"/>
+      <c r="D17" s="405"/>
+      <c r="E17" s="405"/>
+      <c r="F17" s="405"/>
+      <c r="G17" s="405"/>
+      <c r="H17" s="405"/>
+      <c r="I17" s="405"/>
+      <c r="J17" s="405"/>
+      <c r="K17" s="405"/>
+      <c r="L17" s="406"/>
     </row>
     <row r="18" spans="1:14" s="56" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="235" t="s">
         <v>477</v>
       </c>
-      <c r="B18" s="354" t="s">
+      <c r="B18" s="403" t="s">
         <v>465</v>
       </c>
-      <c r="C18" s="354"/>
-      <c r="D18" s="354"/>
-      <c r="E18" s="354"/>
-      <c r="F18" s="354"/>
-      <c r="G18" s="354"/>
-      <c r="H18" s="354"/>
-      <c r="I18" s="354"/>
-      <c r="J18" s="354"/>
-      <c r="K18" s="354"/>
-      <c r="L18" s="355"/>
+      <c r="C18" s="403"/>
+      <c r="D18" s="403"/>
+      <c r="E18" s="403"/>
+      <c r="F18" s="403"/>
+      <c r="G18" s="403"/>
+      <c r="H18" s="403"/>
+      <c r="I18" s="403"/>
+      <c r="J18" s="403"/>
+      <c r="K18" s="403"/>
+      <c r="L18" s="404"/>
     </row>
     <row r="19" spans="1:14" s="57" customFormat="1" ht="269" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="227"/>
@@ -20168,12 +18986,12 @@
       <c r="L19" s="234"/>
     </row>
     <row r="20" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="352" t="s">
+      <c r="A20" s="401" t="s">
         <v>343</v>
       </c>
-      <c r="B20" s="353"/>
-      <c r="C20" s="353"/>
-      <c r="D20" s="353"/>
+      <c r="B20" s="402"/>
+      <c r="C20" s="402"/>
+      <c r="D20" s="402"/>
       <c r="E20" s="232" t="s">
         <v>344</v>
       </c>
@@ -20200,84 +19018,84 @@
       <c r="L21" s="110"/>
     </row>
     <row r="22" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="386" t="s">
+      <c r="A22" s="364" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="387"/>
-      <c r="C22" s="387"/>
-      <c r="D22" s="387"/>
-      <c r="E22" s="387"/>
-      <c r="F22" s="387"/>
-      <c r="G22" s="387"/>
-      <c r="H22" s="387"/>
-      <c r="I22" s="387"/>
-      <c r="J22" s="387"/>
-      <c r="K22" s="387"/>
-      <c r="L22" s="388"/>
+      <c r="B22" s="365"/>
+      <c r="C22" s="365"/>
+      <c r="D22" s="365"/>
+      <c r="E22" s="365"/>
+      <c r="F22" s="365"/>
+      <c r="G22" s="365"/>
+      <c r="H22" s="365"/>
+      <c r="I22" s="365"/>
+      <c r="J22" s="365"/>
+      <c r="K22" s="365"/>
+      <c r="L22" s="366"/>
     </row>
     <row r="23" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="389" t="s">
+      <c r="A23" s="367" t="s">
         <v>281</v>
       </c>
-      <c r="B23" s="390"/>
-      <c r="C23" s="390"/>
-      <c r="D23" s="390"/>
-      <c r="E23" s="390"/>
-      <c r="F23" s="390"/>
-      <c r="G23" s="390"/>
-      <c r="H23" s="390"/>
-      <c r="I23" s="390"/>
-      <c r="J23" s="390"/>
-      <c r="K23" s="390"/>
-      <c r="L23" s="391"/>
+      <c r="B23" s="368"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="368"/>
+      <c r="E23" s="368"/>
+      <c r="F23" s="368"/>
+      <c r="G23" s="368"/>
+      <c r="H23" s="368"/>
+      <c r="I23" s="368"/>
+      <c r="J23" s="368"/>
+      <c r="K23" s="368"/>
+      <c r="L23" s="369"/>
     </row>
     <row r="24" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="392" t="s">
+      <c r="A24" s="370" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="368"/>
-      <c r="C24" s="368"/>
-      <c r="D24" s="368"/>
-      <c r="E24" s="368"/>
-      <c r="F24" s="368"/>
-      <c r="G24" s="368"/>
-      <c r="H24" s="368"/>
-      <c r="I24" s="368"/>
-      <c r="J24" s="368"/>
-      <c r="K24" s="368"/>
-      <c r="L24" s="369"/>
+      <c r="B24" s="371"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="371"/>
+      <c r="E24" s="371"/>
+      <c r="F24" s="371"/>
+      <c r="G24" s="371"/>
+      <c r="H24" s="371"/>
+      <c r="I24" s="371"/>
+      <c r="J24" s="371"/>
+      <c r="K24" s="371"/>
+      <c r="L24" s="372"/>
     </row>
     <row r="25" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="392" t="s">
+      <c r="A25" s="370" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="368"/>
-      <c r="C25" s="368"/>
-      <c r="D25" s="368"/>
-      <c r="E25" s="368"/>
-      <c r="F25" s="368"/>
-      <c r="G25" s="368"/>
-      <c r="H25" s="368"/>
-      <c r="I25" s="368"/>
-      <c r="J25" s="368"/>
-      <c r="K25" s="368"/>
-      <c r="L25" s="369"/>
+      <c r="B25" s="371"/>
+      <c r="C25" s="371"/>
+      <c r="D25" s="371"/>
+      <c r="E25" s="371"/>
+      <c r="F25" s="371"/>
+      <c r="G25" s="371"/>
+      <c r="H25" s="371"/>
+      <c r="I25" s="371"/>
+      <c r="J25" s="371"/>
+      <c r="K25" s="371"/>
+      <c r="L25" s="372"/>
     </row>
     <row r="26" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="393" t="s">
+      <c r="A26" s="373" t="s">
         <v>283</v>
       </c>
-      <c r="B26" s="394"/>
-      <c r="C26" s="394"/>
-      <c r="D26" s="394"/>
-      <c r="E26" s="394"/>
-      <c r="F26" s="394"/>
-      <c r="G26" s="394"/>
-      <c r="H26" s="394"/>
-      <c r="I26" s="394"/>
-      <c r="J26" s="394"/>
-      <c r="K26" s="394"/>
-      <c r="L26" s="395"/>
+      <c r="B26" s="374"/>
+      <c r="C26" s="374"/>
+      <c r="D26" s="374"/>
+      <c r="E26" s="374"/>
+      <c r="F26" s="374"/>
+      <c r="G26" s="374"/>
+      <c r="H26" s="374"/>
+      <c r="I26" s="374"/>
+      <c r="J26" s="374"/>
+      <c r="K26" s="374"/>
+      <c r="L26" s="375"/>
     </row>
     <row r="27" spans="1:14" s="57" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="110"/>
@@ -20294,332 +19112,332 @@
       <c r="L27" s="110"/>
     </row>
     <row r="28" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="396" t="s">
+      <c r="A28" s="376" t="s">
         <v>279</v>
       </c>
-      <c r="B28" s="397"/>
-      <c r="C28" s="397"/>
-      <c r="D28" s="397"/>
-      <c r="E28" s="397"/>
-      <c r="F28" s="397"/>
-      <c r="G28" s="397"/>
-      <c r="H28" s="397"/>
-      <c r="I28" s="397"/>
-      <c r="J28" s="397"/>
-      <c r="K28" s="397"/>
-      <c r="L28" s="398"/>
+      <c r="B28" s="377"/>
+      <c r="C28" s="377"/>
+      <c r="D28" s="377"/>
+      <c r="E28" s="377"/>
+      <c r="F28" s="377"/>
+      <c r="G28" s="377"/>
+      <c r="H28" s="377"/>
+      <c r="I28" s="377"/>
+      <c r="J28" s="377"/>
+      <c r="K28" s="377"/>
+      <c r="L28" s="378"/>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="375" t="s">
+      <c r="A29" s="353" t="s">
         <v>175</v>
       </c>
-      <c r="B29" s="376"/>
-      <c r="C29" s="376"/>
-      <c r="D29" s="376"/>
-      <c r="E29" s="376"/>
-      <c r="F29" s="376"/>
-      <c r="G29" s="376"/>
-      <c r="H29" s="376"/>
-      <c r="I29" s="376"/>
-      <c r="J29" s="376"/>
-      <c r="K29" s="376"/>
-      <c r="L29" s="377"/>
+      <c r="B29" s="354"/>
+      <c r="C29" s="354"/>
+      <c r="D29" s="354"/>
+      <c r="E29" s="354"/>
+      <c r="F29" s="354"/>
+      <c r="G29" s="354"/>
+      <c r="H29" s="354"/>
+      <c r="I29" s="354"/>
+      <c r="J29" s="354"/>
+      <c r="K29" s="354"/>
+      <c r="L29" s="355"/>
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="209">
         <v>1</v>
       </c>
-      <c r="B30" s="361" t="s">
+      <c r="B30" s="388" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="361"/>
-      <c r="D30" s="361"/>
-      <c r="E30" s="361"/>
-      <c r="F30" s="361"/>
-      <c r="G30" s="361"/>
-      <c r="H30" s="361"/>
-      <c r="I30" s="361"/>
-      <c r="J30" s="361"/>
-      <c r="K30" s="361"/>
-      <c r="L30" s="362"/>
+      <c r="C30" s="388"/>
+      <c r="D30" s="388"/>
+      <c r="E30" s="388"/>
+      <c r="F30" s="388"/>
+      <c r="G30" s="388"/>
+      <c r="H30" s="388"/>
+      <c r="I30" s="388"/>
+      <c r="J30" s="388"/>
+      <c r="K30" s="388"/>
+      <c r="L30" s="389"/>
     </row>
     <row r="31" spans="1:14" s="57" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="209">
         <v>2</v>
       </c>
-      <c r="B31" s="361" t="s">
+      <c r="B31" s="388" t="s">
         <v>275</v>
       </c>
-      <c r="C31" s="361"/>
-      <c r="D31" s="361"/>
-      <c r="E31" s="361"/>
-      <c r="F31" s="361"/>
-      <c r="G31" s="361"/>
-      <c r="H31" s="361"/>
-      <c r="I31" s="361"/>
-      <c r="J31" s="361"/>
-      <c r="K31" s="361"/>
-      <c r="L31" s="362"/>
+      <c r="C31" s="388"/>
+      <c r="D31" s="388"/>
+      <c r="E31" s="388"/>
+      <c r="F31" s="388"/>
+      <c r="G31" s="388"/>
+      <c r="H31" s="388"/>
+      <c r="I31" s="388"/>
+      <c r="J31" s="388"/>
+      <c r="K31" s="388"/>
+      <c r="L31" s="389"/>
       <c r="N31" s="104"/>
     </row>
     <row r="32" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="209">
         <v>3</v>
       </c>
-      <c r="B32" s="361" t="s">
+      <c r="B32" s="388" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="361"/>
-      <c r="D32" s="361"/>
-      <c r="E32" s="361"/>
-      <c r="F32" s="361"/>
-      <c r="G32" s="361"/>
-      <c r="H32" s="361"/>
-      <c r="I32" s="361"/>
-      <c r="J32" s="361"/>
-      <c r="K32" s="361"/>
-      <c r="L32" s="362"/>
+      <c r="C32" s="388"/>
+      <c r="D32" s="388"/>
+      <c r="E32" s="388"/>
+      <c r="F32" s="388"/>
+      <c r="G32" s="388"/>
+      <c r="H32" s="388"/>
+      <c r="I32" s="388"/>
+      <c r="J32" s="388"/>
+      <c r="K32" s="388"/>
+      <c r="L32" s="389"/>
       <c r="N32" s="104"/>
     </row>
     <row r="33" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="209">
         <v>4</v>
       </c>
-      <c r="B33" s="361" t="s">
+      <c r="B33" s="388" t="s">
         <v>284</v>
       </c>
-      <c r="C33" s="361"/>
-      <c r="D33" s="361"/>
-      <c r="E33" s="361"/>
-      <c r="F33" s="361"/>
-      <c r="G33" s="361"/>
-      <c r="H33" s="361"/>
-      <c r="I33" s="361"/>
-      <c r="J33" s="361"/>
-      <c r="K33" s="361"/>
-      <c r="L33" s="362"/>
+      <c r="C33" s="388"/>
+      <c r="D33" s="388"/>
+      <c r="E33" s="388"/>
+      <c r="F33" s="388"/>
+      <c r="G33" s="388"/>
+      <c r="H33" s="388"/>
+      <c r="I33" s="388"/>
+      <c r="J33" s="388"/>
+      <c r="K33" s="388"/>
+      <c r="L33" s="389"/>
       <c r="N33" s="104"/>
     </row>
     <row r="34" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="209">
         <v>5</v>
       </c>
-      <c r="B34" s="361" t="s">
+      <c r="B34" s="388" t="s">
         <v>168</v>
       </c>
-      <c r="C34" s="361"/>
-      <c r="D34" s="361"/>
-      <c r="E34" s="361"/>
-      <c r="F34" s="361"/>
-      <c r="G34" s="361"/>
-      <c r="H34" s="361"/>
-      <c r="I34" s="361"/>
-      <c r="J34" s="361"/>
-      <c r="K34" s="361"/>
-      <c r="L34" s="362"/>
+      <c r="C34" s="388"/>
+      <c r="D34" s="388"/>
+      <c r="E34" s="388"/>
+      <c r="F34" s="388"/>
+      <c r="G34" s="388"/>
+      <c r="H34" s="388"/>
+      <c r="I34" s="388"/>
+      <c r="J34" s="388"/>
+      <c r="K34" s="388"/>
+      <c r="L34" s="389"/>
       <c r="N34" s="104"/>
     </row>
     <row r="35" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="209"/>
-      <c r="B35" s="361" t="s">
+      <c r="B35" s="388" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="361"/>
-      <c r="D35" s="361"/>
-      <c r="E35" s="361"/>
-      <c r="F35" s="361"/>
-      <c r="G35" s="361"/>
-      <c r="H35" s="361"/>
-      <c r="I35" s="361"/>
-      <c r="J35" s="361"/>
-      <c r="K35" s="361"/>
-      <c r="L35" s="362"/>
+      <c r="C35" s="388"/>
+      <c r="D35" s="388"/>
+      <c r="E35" s="388"/>
+      <c r="F35" s="388"/>
+      <c r="G35" s="388"/>
+      <c r="H35" s="388"/>
+      <c r="I35" s="388"/>
+      <c r="J35" s="388"/>
+      <c r="K35" s="388"/>
+      <c r="L35" s="389"/>
       <c r="N35" s="104"/>
     </row>
     <row r="36" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="209"/>
-      <c r="B36" s="361" t="s">
+      <c r="B36" s="388" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
-      <c r="G36" s="361"/>
-      <c r="H36" s="361"/>
-      <c r="I36" s="361"/>
-      <c r="J36" s="361"/>
-      <c r="K36" s="361"/>
-      <c r="L36" s="362"/>
+      <c r="C36" s="388"/>
+      <c r="D36" s="388"/>
+      <c r="E36" s="388"/>
+      <c r="F36" s="388"/>
+      <c r="G36" s="388"/>
+      <c r="H36" s="388"/>
+      <c r="I36" s="388"/>
+      <c r="J36" s="388"/>
+      <c r="K36" s="388"/>
+      <c r="L36" s="389"/>
       <c r="N36" s="104"/>
     </row>
     <row r="37" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="370" t="s">
+      <c r="A37" s="390" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="371"/>
-      <c r="C37" s="371"/>
-      <c r="D37" s="371"/>
-      <c r="E37" s="371"/>
-      <c r="F37" s="371"/>
-      <c r="G37" s="371"/>
-      <c r="H37" s="371"/>
-      <c r="I37" s="371"/>
-      <c r="J37" s="371"/>
-      <c r="K37" s="371"/>
-      <c r="L37" s="372"/>
+      <c r="B37" s="391"/>
+      <c r="C37" s="391"/>
+      <c r="D37" s="391"/>
+      <c r="E37" s="391"/>
+      <c r="F37" s="391"/>
+      <c r="G37" s="391"/>
+      <c r="H37" s="391"/>
+      <c r="I37" s="391"/>
+      <c r="J37" s="391"/>
+      <c r="K37" s="391"/>
+      <c r="L37" s="392"/>
       <c r="N37" s="104"/>
     </row>
     <row r="38" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="209">
         <v>1</v>
       </c>
-      <c r="B38" s="361" t="s">
+      <c r="B38" s="388" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="361"/>
-      <c r="D38" s="361"/>
-      <c r="E38" s="361"/>
-      <c r="F38" s="361"/>
-      <c r="G38" s="361"/>
-      <c r="H38" s="361"/>
-      <c r="I38" s="361"/>
-      <c r="J38" s="361"/>
-      <c r="K38" s="361"/>
-      <c r="L38" s="362"/>
+      <c r="C38" s="388"/>
+      <c r="D38" s="388"/>
+      <c r="E38" s="388"/>
+      <c r="F38" s="388"/>
+      <c r="G38" s="388"/>
+      <c r="H38" s="388"/>
+      <c r="I38" s="388"/>
+      <c r="J38" s="388"/>
+      <c r="K38" s="388"/>
+      <c r="L38" s="389"/>
       <c r="N38" s="104"/>
     </row>
     <row r="39" spans="1:14" s="57" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="209"/>
-      <c r="B39" s="359" t="s">
+      <c r="B39" s="386" t="s">
         <v>426</v>
       </c>
-      <c r="C39" s="359"/>
-      <c r="D39" s="359"/>
-      <c r="E39" s="359"/>
-      <c r="F39" s="359"/>
-      <c r="G39" s="359"/>
-      <c r="H39" s="359"/>
-      <c r="I39" s="359"/>
-      <c r="J39" s="359"/>
-      <c r="K39" s="359"/>
-      <c r="L39" s="360"/>
+      <c r="C39" s="386"/>
+      <c r="D39" s="386"/>
+      <c r="E39" s="386"/>
+      <c r="F39" s="386"/>
+      <c r="G39" s="386"/>
+      <c r="H39" s="386"/>
+      <c r="I39" s="386"/>
+      <c r="J39" s="386"/>
+      <c r="K39" s="386"/>
+      <c r="L39" s="387"/>
       <c r="N39" s="104"/>
     </row>
     <row r="40" spans="1:14" s="57" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="209">
         <v>2</v>
       </c>
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="388" t="s">
         <v>278</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
-      <c r="G40" s="361"/>
-      <c r="H40" s="361"/>
-      <c r="I40" s="361"/>
-      <c r="J40" s="361"/>
-      <c r="K40" s="361"/>
-      <c r="L40" s="362"/>
+      <c r="C40" s="388"/>
+      <c r="D40" s="388"/>
+      <c r="E40" s="388"/>
+      <c r="F40" s="388"/>
+      <c r="G40" s="388"/>
+      <c r="H40" s="388"/>
+      <c r="I40" s="388"/>
+      <c r="J40" s="388"/>
+      <c r="K40" s="388"/>
+      <c r="L40" s="389"/>
       <c r="N40" s="104"/>
     </row>
     <row r="41" spans="1:14" s="57" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="209">
         <v>3</v>
       </c>
-      <c r="B41" s="361" t="s">
+      <c r="B41" s="388" t="s">
         <v>475</v>
       </c>
-      <c r="C41" s="361"/>
-      <c r="D41" s="361"/>
-      <c r="E41" s="361"/>
-      <c r="F41" s="361"/>
-      <c r="G41" s="361"/>
-      <c r="H41" s="361"/>
-      <c r="I41" s="361"/>
-      <c r="J41" s="361"/>
-      <c r="K41" s="361"/>
-      <c r="L41" s="362"/>
+      <c r="C41" s="388"/>
+      <c r="D41" s="388"/>
+      <c r="E41" s="388"/>
+      <c r="F41" s="388"/>
+      <c r="G41" s="388"/>
+      <c r="H41" s="388"/>
+      <c r="I41" s="388"/>
+      <c r="J41" s="388"/>
+      <c r="K41" s="388"/>
+      <c r="L41" s="389"/>
       <c r="N41" s="104"/>
     </row>
     <row r="42" spans="1:14" s="57" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="209">
         <v>4</v>
       </c>
-      <c r="B42" s="361" t="s">
+      <c r="B42" s="388" t="s">
         <v>285</v>
       </c>
-      <c r="C42" s="361"/>
-      <c r="D42" s="361"/>
-      <c r="E42" s="361"/>
-      <c r="F42" s="361"/>
-      <c r="G42" s="361"/>
-      <c r="H42" s="361"/>
-      <c r="I42" s="361"/>
-      <c r="J42" s="361"/>
-      <c r="K42" s="361"/>
-      <c r="L42" s="362"/>
+      <c r="C42" s="388"/>
+      <c r="D42" s="388"/>
+      <c r="E42" s="388"/>
+      <c r="F42" s="388"/>
+      <c r="G42" s="388"/>
+      <c r="H42" s="388"/>
+      <c r="I42" s="388"/>
+      <c r="J42" s="388"/>
+      <c r="K42" s="388"/>
+      <c r="L42" s="389"/>
       <c r="N42" s="104"/>
     </row>
     <row r="43" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="209">
         <v>5</v>
       </c>
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="386" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-      <c r="G43" s="359"/>
-      <c r="H43" s="359"/>
-      <c r="I43" s="359"/>
-      <c r="J43" s="359"/>
-      <c r="K43" s="359"/>
-      <c r="L43" s="360"/>
+      <c r="C43" s="386"/>
+      <c r="D43" s="386"/>
+      <c r="E43" s="386"/>
+      <c r="F43" s="386"/>
+      <c r="G43" s="386"/>
+      <c r="H43" s="386"/>
+      <c r="I43" s="386"/>
+      <c r="J43" s="386"/>
+      <c r="K43" s="386"/>
+      <c r="L43" s="387"/>
       <c r="N43" s="104"/>
     </row>
     <row r="44" spans="1:14" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="209">
         <v>6</v>
       </c>
-      <c r="B44" s="359" t="s">
+      <c r="B44" s="386" t="s">
         <v>476</v>
       </c>
-      <c r="C44" s="359"/>
-      <c r="D44" s="359"/>
-      <c r="E44" s="359"/>
-      <c r="F44" s="359"/>
-      <c r="G44" s="359"/>
-      <c r="H44" s="359"/>
-      <c r="I44" s="359"/>
-      <c r="J44" s="359"/>
-      <c r="K44" s="359"/>
-      <c r="L44" s="360"/>
+      <c r="C44" s="386"/>
+      <c r="D44" s="386"/>
+      <c r="E44" s="386"/>
+      <c r="F44" s="386"/>
+      <c r="G44" s="386"/>
+      <c r="H44" s="386"/>
+      <c r="I44" s="386"/>
+      <c r="J44" s="386"/>
+      <c r="K44" s="386"/>
+      <c r="L44" s="387"/>
       <c r="N44" s="104"/>
     </row>
     <row r="45" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="209">
         <v>7</v>
       </c>
-      <c r="B45" s="361" t="s">
+      <c r="B45" s="388" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="361"/>
-      <c r="D45" s="361"/>
-      <c r="E45" s="361"/>
-      <c r="F45" s="361"/>
-      <c r="G45" s="361"/>
-      <c r="H45" s="361"/>
-      <c r="I45" s="361"/>
-      <c r="J45" s="361"/>
-      <c r="K45" s="361"/>
-      <c r="L45" s="362"/>
+      <c r="C45" s="388"/>
+      <c r="D45" s="388"/>
+      <c r="E45" s="388"/>
+      <c r="F45" s="388"/>
+      <c r="G45" s="388"/>
+      <c r="H45" s="388"/>
+      <c r="I45" s="388"/>
+      <c r="J45" s="388"/>
+      <c r="K45" s="388"/>
+      <c r="L45" s="389"/>
     </row>
     <row r="46" spans="1:14" s="57" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="209"/>
@@ -20636,56 +19454,56 @@
       <c r="L46" s="211"/>
     </row>
     <row r="47" spans="1:14" s="57" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="370" t="s">
+      <c r="A47" s="390" t="s">
         <v>273</v>
       </c>
-      <c r="B47" s="371"/>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
-      <c r="G47" s="371"/>
-      <c r="H47" s="371"/>
-      <c r="I47" s="371"/>
-      <c r="J47" s="371"/>
-      <c r="K47" s="371"/>
-      <c r="L47" s="372"/>
+      <c r="B47" s="391"/>
+      <c r="C47" s="391"/>
+      <c r="D47" s="391"/>
+      <c r="E47" s="391"/>
+      <c r="F47" s="391"/>
+      <c r="G47" s="391"/>
+      <c r="H47" s="391"/>
+      <c r="I47" s="391"/>
+      <c r="J47" s="391"/>
+      <c r="K47" s="391"/>
+      <c r="L47" s="392"/>
     </row>
     <row r="48" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="212" t="s">
         <v>271</v>
       </c>
-      <c r="B48" s="361" t="s">
+      <c r="B48" s="388" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="361"/>
-      <c r="D48" s="361"/>
-      <c r="E48" s="361"/>
-      <c r="F48" s="361"/>
-      <c r="G48" s="361"/>
-      <c r="H48" s="361"/>
-      <c r="I48" s="361"/>
-      <c r="J48" s="361"/>
-      <c r="K48" s="361"/>
-      <c r="L48" s="362"/>
+      <c r="C48" s="388"/>
+      <c r="D48" s="388"/>
+      <c r="E48" s="388"/>
+      <c r="F48" s="388"/>
+      <c r="G48" s="388"/>
+      <c r="H48" s="388"/>
+      <c r="I48" s="388"/>
+      <c r="J48" s="388"/>
+      <c r="K48" s="388"/>
+      <c r="L48" s="389"/>
     </row>
     <row r="49" spans="1:12" s="57" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="B49" s="363" t="s">
+      <c r="B49" s="394" t="s">
         <v>274</v>
       </c>
-      <c r="C49" s="363"/>
-      <c r="D49" s="363"/>
-      <c r="E49" s="363"/>
-      <c r="F49" s="363"/>
-      <c r="G49" s="363"/>
-      <c r="H49" s="363"/>
-      <c r="I49" s="363"/>
-      <c r="J49" s="363"/>
-      <c r="K49" s="363"/>
-      <c r="L49" s="364"/>
+      <c r="C49" s="394"/>
+      <c r="D49" s="394"/>
+      <c r="E49" s="394"/>
+      <c r="F49" s="394"/>
+      <c r="G49" s="394"/>
+      <c r="H49" s="394"/>
+      <c r="I49" s="394"/>
+      <c r="J49" s="394"/>
+      <c r="K49" s="394"/>
+      <c r="L49" s="395"/>
     </row>
     <row r="50" spans="1:12" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="157"/>
@@ -20702,20 +19520,20 @@
       <c r="L50" s="110"/>
     </row>
     <row r="51" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="365" t="s">
+      <c r="A51" s="396" t="s">
         <v>200</v>
       </c>
-      <c r="B51" s="366"/>
-      <c r="C51" s="366"/>
-      <c r="D51" s="366"/>
-      <c r="E51" s="366"/>
-      <c r="F51" s="366"/>
-      <c r="G51" s="366"/>
-      <c r="H51" s="366"/>
-      <c r="I51" s="366"/>
-      <c r="J51" s="366"/>
-      <c r="K51" s="366"/>
-      <c r="L51" s="367"/>
+      <c r="B51" s="397"/>
+      <c r="C51" s="397"/>
+      <c r="D51" s="397"/>
+      <c r="E51" s="397"/>
+      <c r="F51" s="397"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="397"/>
+      <c r="I51" s="397"/>
+      <c r="J51" s="397"/>
+      <c r="K51" s="397"/>
+      <c r="L51" s="398"/>
     </row>
     <row r="52" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="216" t="s">
@@ -20803,126 +19621,126 @@
       <c r="B57" s="165" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="368" t="s">
+      <c r="C57" s="371" t="s">
         <v>262</v>
       </c>
-      <c r="D57" s="368"/>
-      <c r="E57" s="368"/>
-      <c r="F57" s="368"/>
-      <c r="G57" s="368"/>
-      <c r="H57" s="368"/>
-      <c r="I57" s="368"/>
-      <c r="J57" s="368"/>
-      <c r="K57" s="368"/>
-      <c r="L57" s="369"/>
+      <c r="D57" s="371"/>
+      <c r="E57" s="371"/>
+      <c r="F57" s="371"/>
+      <c r="G57" s="371"/>
+      <c r="H57" s="371"/>
+      <c r="I57" s="371"/>
+      <c r="J57" s="371"/>
+      <c r="K57" s="371"/>
+      <c r="L57" s="372"/>
     </row>
     <row r="58" spans="1:12" s="56" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="164"/>
       <c r="B58" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="C58" s="368" t="s">
+      <c r="C58" s="371" t="s">
         <v>264</v>
       </c>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
-      <c r="G58" s="368"/>
-      <c r="H58" s="368"/>
-      <c r="I58" s="368"/>
-      <c r="J58" s="368"/>
-      <c r="K58" s="368"/>
-      <c r="L58" s="369"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
+      <c r="G58" s="371"/>
+      <c r="H58" s="371"/>
+      <c r="I58" s="371"/>
+      <c r="J58" s="371"/>
+      <c r="K58" s="371"/>
+      <c r="L58" s="372"/>
     </row>
     <row r="59" spans="1:12" s="56" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="164"/>
       <c r="B59" s="165" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="368" t="s">
+      <c r="C59" s="371" t="s">
         <v>328</v>
       </c>
-      <c r="D59" s="368"/>
-      <c r="E59" s="368"/>
-      <c r="F59" s="368"/>
-      <c r="G59" s="368"/>
-      <c r="H59" s="368"/>
-      <c r="I59" s="368"/>
-      <c r="J59" s="368"/>
-      <c r="K59" s="368"/>
-      <c r="L59" s="369"/>
+      <c r="D59" s="371"/>
+      <c r="E59" s="371"/>
+      <c r="F59" s="371"/>
+      <c r="G59" s="371"/>
+      <c r="H59" s="371"/>
+      <c r="I59" s="371"/>
+      <c r="J59" s="371"/>
+      <c r="K59" s="371"/>
+      <c r="L59" s="372"/>
     </row>
     <row r="60" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="164"/>
       <c r="B60" s="165" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="368" t="s">
+      <c r="C60" s="371" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="368"/>
-      <c r="E60" s="368"/>
-      <c r="F60" s="368"/>
-      <c r="G60" s="368"/>
-      <c r="H60" s="368"/>
-      <c r="I60" s="368"/>
-      <c r="J60" s="368"/>
-      <c r="K60" s="368"/>
-      <c r="L60" s="369"/>
+      <c r="D60" s="371"/>
+      <c r="E60" s="371"/>
+      <c r="F60" s="371"/>
+      <c r="G60" s="371"/>
+      <c r="H60" s="371"/>
+      <c r="I60" s="371"/>
+      <c r="J60" s="371"/>
+      <c r="K60" s="371"/>
+      <c r="L60" s="372"/>
     </row>
     <row r="61" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="164"/>
       <c r="B61" s="165" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="368" t="s">
+      <c r="C61" s="371" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="368"/>
-      <c r="E61" s="368"/>
-      <c r="F61" s="368"/>
-      <c r="G61" s="368"/>
-      <c r="H61" s="368"/>
-      <c r="I61" s="368"/>
-      <c r="J61" s="368"/>
-      <c r="K61" s="368"/>
-      <c r="L61" s="369"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
+      <c r="G61" s="371"/>
+      <c r="H61" s="371"/>
+      <c r="I61" s="371"/>
+      <c r="J61" s="371"/>
+      <c r="K61" s="371"/>
+      <c r="L61" s="372"/>
     </row>
     <row r="62" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="164"/>
       <c r="B62" s="165" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="368" t="s">
+      <c r="C62" s="371" t="s">
         <v>466</v>
       </c>
-      <c r="D62" s="373"/>
-      <c r="E62" s="373"/>
-      <c r="F62" s="373"/>
-      <c r="G62" s="373"/>
-      <c r="H62" s="373"/>
-      <c r="I62" s="373"/>
-      <c r="J62" s="373"/>
-      <c r="K62" s="373"/>
-      <c r="L62" s="374"/>
+      <c r="D62" s="399"/>
+      <c r="E62" s="399"/>
+      <c r="F62" s="399"/>
+      <c r="G62" s="399"/>
+      <c r="H62" s="399"/>
+      <c r="I62" s="399"/>
+      <c r="J62" s="399"/>
+      <c r="K62" s="399"/>
+      <c r="L62" s="400"/>
     </row>
     <row r="63" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="164"/>
       <c r="B63" s="165" t="s">
         <v>393</v>
       </c>
-      <c r="C63" s="368" t="s">
+      <c r="C63" s="371" t="s">
         <v>394</v>
       </c>
-      <c r="D63" s="368"/>
-      <c r="E63" s="368"/>
-      <c r="F63" s="368"/>
-      <c r="G63" s="368"/>
-      <c r="H63" s="368"/>
-      <c r="I63" s="368"/>
-      <c r="J63" s="368"/>
-      <c r="K63" s="368"/>
-      <c r="L63" s="369"/>
+      <c r="D63" s="371"/>
+      <c r="E63" s="371"/>
+      <c r="F63" s="371"/>
+      <c r="G63" s="371"/>
+      <c r="H63" s="371"/>
+      <c r="I63" s="371"/>
+      <c r="J63" s="371"/>
+      <c r="K63" s="371"/>
+      <c r="L63" s="372"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="164"/>
@@ -21040,25 +19858,58 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="358" t="s">
+      <c r="A85" s="393" t="s">
         <v>397</v>
       </c>
-      <c r="B85" s="358"/>
-      <c r="C85" s="358"/>
-      <c r="D85" s="358"/>
-      <c r="E85" s="358"/>
-      <c r="F85" s="358"/>
-      <c r="G85" s="358"/>
-      <c r="H85" s="358"/>
-      <c r="I85" s="358"/>
-      <c r="J85" s="358"/>
-      <c r="K85" s="358"/>
-      <c r="L85" s="358"/>
+      <c r="B85" s="393"/>
+      <c r="C85" s="393"/>
+      <c r="D85" s="393"/>
+      <c r="E85" s="393"/>
+      <c r="F85" s="393"/>
+      <c r="G85" s="393"/>
+      <c r="H85" s="393"/>
+      <c r="I85" s="393"/>
+      <c r="J85" s="393"/>
+      <c r="K85" s="393"/>
+      <c r="L85" s="393"/>
     </row>
     <row r="90" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="91" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="B17:L17"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="B44:L44"/>
+    <mergeCell ref="B45:L45"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="B49:L49"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="C60:L60"/>
+    <mergeCell ref="C61:L61"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C63:L63"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="C59:L59"/>
+    <mergeCell ref="C62:L62"/>
+    <mergeCell ref="B43:L43"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B35:L35"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B39:L39"/>
+    <mergeCell ref="B41:L41"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A4:L4"/>
@@ -21075,39 +19926,6 @@
     <mergeCell ref="B8:L8"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="B31:L31"/>
-    <mergeCell ref="B32:L32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B39:L39"/>
-    <mergeCell ref="B41:L41"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="A85:L85"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="B45:L45"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="B49:L49"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="C60:L60"/>
-    <mergeCell ref="C61:L61"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C63:L63"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="C59:L59"/>
-    <mergeCell ref="C62:L62"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B16:L16"/>
-    <mergeCell ref="B17:L17"/>
-    <mergeCell ref="B18:L18"/>
-    <mergeCell ref="B14:L14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A70" r:id="rId1" xr:uid="{C9866D44-2827-49D7-B9C3-89CF23FACDC1}"/>
@@ -21141,82 +19959,82 @@
       </c>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="450" t="s">
+      <c r="A3" s="451" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="450"/>
-      <c r="C3" s="450"/>
+      <c r="B3" s="451"/>
+      <c r="C3" s="451"/>
       <c r="D3" s="125" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="451" t="s">
+      <c r="A4" s="452" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="451"/>
-      <c r="C4" s="451"/>
+      <c r="B4" s="452"/>
+      <c r="C4" s="452"/>
       <c r="D4" s="172" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="455" t="s">
+      <c r="A5" s="456" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="452"/>
-      <c r="C5" s="452"/>
+      <c r="B5" s="453"/>
+      <c r="C5" s="453"/>
       <c r="D5" s="173" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="453" t="s">
+      <c r="A6" s="454" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="453"/>
-      <c r="C6" s="453"/>
+      <c r="B6" s="454"/>
+      <c r="C6" s="454"/>
       <c r="D6" s="174" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="454" t="s">
+      <c r="A7" s="455" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="454"/>
-      <c r="C7" s="454"/>
+      <c r="B7" s="455"/>
+      <c r="C7" s="455"/>
       <c r="D7" s="175" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="451" t="s">
+      <c r="A11" s="452" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="451"/>
-      <c r="C11" s="451"/>
+      <c r="B11" s="452"/>
+      <c r="C11" s="452"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="452" t="s">
+      <c r="A12" s="453" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="452"/>
-      <c r="C12" s="452"/>
+      <c r="B12" s="453"/>
+      <c r="C12" s="453"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="453" t="s">
+      <c r="A13" s="454" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="453"/>
-      <c r="C13" s="453"/>
+      <c r="B13" s="454"/>
+      <c r="C13" s="454"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="454" t="s">
+      <c r="A14" s="455" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="454"/>
-      <c r="C14" s="454"/>
+      <c r="B14" s="455"/>
+      <c r="C14" s="455"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -21575,21 +20393,21 @@
         <v>3.1563530000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="458" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="459"/>
-      <c r="C6" s="459"/>
-      <c r="D6" s="459"/>
-      <c r="E6" s="459"/>
-      <c r="F6" s="459"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="352"/>
+      <c r="C6" s="352"/>
+      <c r="D6" s="352"/>
+      <c r="E6" s="352"/>
+      <c r="F6" s="352"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B7" s="460" t="s">
+      <c r="B7" s="457" t="s">
         <v>485</v>
       </c>
-      <c r="C7" s="460"/>
-      <c r="D7" s="460"/>
-      <c r="E7" s="460"/>
-      <c r="F7" s="460"/>
+      <c r="C7" s="457"/>
+      <c r="D7" s="457"/>
+      <c r="E7" s="457"/>
+      <c r="F7" s="457"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="101" t="s">
@@ -21751,13 +20569,13 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="460" t="s">
+      <c r="B16" s="457" t="s">
         <v>487</v>
       </c>
-      <c r="C16" s="460"/>
-      <c r="D16" s="460"/>
-      <c r="E16" s="460"/>
-      <c r="F16" s="460"/>
+      <c r="C16" s="457"/>
+      <c r="D16" s="457"/>
+      <c r="E16" s="457"/>
+      <c r="F16" s="457"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="101" t="s">
@@ -21933,28 +20751,28 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="456" t="s">
+      <c r="A2" s="458" t="s">
         <v>420</v>
       </c>
-      <c r="B2" s="457"/>
-      <c r="C2" s="457"/>
-      <c r="D2" s="457"/>
-      <c r="E2" s="457"/>
-      <c r="F2" s="457"/>
-      <c r="G2" s="457"/>
-      <c r="H2" s="457"/>
-      <c r="I2" s="457"/>
-      <c r="J2" s="457"/>
-      <c r="K2" s="457"/>
-      <c r="L2" s="457"/>
-      <c r="M2" s="457"/>
-      <c r="N2" s="457"/>
-      <c r="O2" s="457"/>
-      <c r="P2" s="457"/>
-      <c r="Q2" s="457"/>
-      <c r="R2" s="457"/>
-      <c r="S2" s="457"/>
-      <c r="T2" s="457"/>
+      <c r="B2" s="459"/>
+      <c r="C2" s="459"/>
+      <c r="D2" s="459"/>
+      <c r="E2" s="459"/>
+      <c r="F2" s="459"/>
+      <c r="G2" s="459"/>
+      <c r="H2" s="459"/>
+      <c r="I2" s="459"/>
+      <c r="J2" s="459"/>
+      <c r="K2" s="459"/>
+      <c r="L2" s="459"/>
+      <c r="M2" s="459"/>
+      <c r="N2" s="459"/>
+      <c r="O2" s="459"/>
+      <c r="P2" s="459"/>
+      <c r="Q2" s="459"/>
+      <c r="R2" s="459"/>
+      <c r="S2" s="459"/>
+      <c r="T2" s="459"/>
     </row>
     <row r="3" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -23346,16 +22164,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="406" t="str">
+      <c r="A1" s="407" t="str">
         <f>'ReadMe-Directions'!A1</f>
         <v>Immersive Model for Lake Mead based on the Principle of Divide Reservoir Inflow</v>
       </c>
-      <c r="B1" s="406"/>
-      <c r="C1" s="406"/>
-      <c r="D1" s="406"/>
-      <c r="E1" s="406"/>
-      <c r="F1" s="406"/>
-      <c r="G1" s="406"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="407"/>
+      <c r="D1" s="407"/>
+      <c r="E1" s="407"/>
+      <c r="F1" s="407"/>
+      <c r="G1" s="407"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -23364,15 +22182,15 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="414" t="s">
+      <c r="A3" s="415" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="414"/>
-      <c r="C3" s="414"/>
-      <c r="D3" s="414"/>
-      <c r="E3" s="414"/>
-      <c r="F3" s="414"/>
-      <c r="G3" s="414"/>
+      <c r="B3" s="415"/>
+      <c r="C3" s="415"/>
+      <c r="D3" s="415"/>
+      <c r="E3" s="415"/>
+      <c r="F3" s="415"/>
+      <c r="G3" s="415"/>
       <c r="H3" s="82"/>
       <c r="I3" s="82"/>
       <c r="J3" s="82"/>
@@ -23388,13 +22206,13 @@
       <c r="B4" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="415" t="s">
+      <c r="C4" s="416" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="416"/>
-      <c r="E4" s="416"/>
-      <c r="F4" s="416"/>
-      <c r="G4" s="417"/>
+      <c r="D4" s="417"/>
+      <c r="E4" s="417"/>
+      <c r="F4" s="417"/>
+      <c r="G4" s="418"/>
       <c r="N4" s="138" t="s">
         <v>329</v>
       </c>
@@ -23404,11 +22222,11 @@
         <v>238</v>
       </c>
       <c r="B5" s="111"/>
-      <c r="C5" s="418"/>
-      <c r="D5" s="413"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="413"/>
+      <c r="C5" s="419"/>
+      <c r="D5" s="414"/>
+      <c r="E5" s="414"/>
+      <c r="F5" s="414"/>
+      <c r="G5" s="414"/>
       <c r="N5" s="138"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,11 +22234,11 @@
         <v>202</v>
       </c>
       <c r="B6" s="111"/>
-      <c r="C6" s="418"/>
-      <c r="D6" s="413"/>
-      <c r="E6" s="413"/>
-      <c r="F6" s="413"/>
-      <c r="G6" s="413"/>
+      <c r="C6" s="419"/>
+      <c r="D6" s="414"/>
+      <c r="E6" s="414"/>
+      <c r="F6" s="414"/>
+      <c r="G6" s="414"/>
       <c r="N6" s="139"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23428,11 +22246,11 @@
         <v>203</v>
       </c>
       <c r="B7" s="111"/>
-      <c r="C7" s="418"/>
-      <c r="D7" s="413"/>
-      <c r="E7" s="413"/>
-      <c r="F7" s="413"/>
-      <c r="G7" s="413"/>
+      <c r="C7" s="419"/>
+      <c r="D7" s="414"/>
+      <c r="E7" s="414"/>
+      <c r="F7" s="414"/>
+      <c r="G7" s="414"/>
       <c r="N7" s="139"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23440,11 +22258,11 @@
         <v>204</v>
       </c>
       <c r="B8" s="88"/>
-      <c r="C8" s="413"/>
-      <c r="D8" s="413"/>
-      <c r="E8" s="413"/>
-      <c r="F8" s="413"/>
-      <c r="G8" s="413"/>
+      <c r="C8" s="414"/>
+      <c r="D8" s="414"/>
+      <c r="E8" s="414"/>
+      <c r="F8" s="414"/>
+      <c r="G8" s="414"/>
       <c r="N8" s="139"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23452,11 +22270,11 @@
         <v>18</v>
       </c>
       <c r="B9" s="88"/>
-      <c r="C9" s="419"/>
-      <c r="D9" s="419"/>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="419"/>
+      <c r="C9" s="420"/>
+      <c r="D9" s="420"/>
+      <c r="E9" s="420"/>
+      <c r="F9" s="420"/>
+      <c r="G9" s="420"/>
       <c r="N9" s="139"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23464,11 +22282,11 @@
         <v>277</v>
       </c>
       <c r="B10" s="88"/>
-      <c r="C10" s="413"/>
-      <c r="D10" s="413"/>
-      <c r="E10" s="413"/>
-      <c r="F10" s="413"/>
-      <c r="G10" s="413"/>
+      <c r="C10" s="414"/>
+      <c r="D10" s="414"/>
+      <c r="E10" s="414"/>
+      <c r="F10" s="414"/>
+      <c r="G10" s="414"/>
       <c r="N10" s="139"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23481,36 +22299,36 @@
       <c r="A12" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="420" t="s">
+      <c r="B12" s="421" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="421"/>
-      <c r="D12" s="422"/>
+      <c r="C12" s="422"/>
+      <c r="D12" s="423"/>
       <c r="N12" s="138" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="423" t="s">
+      <c r="B13" s="424" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="424"/>
-      <c r="D13" s="425"/>
+      <c r="C13" s="425"/>
+      <c r="D13" s="426"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="407" t="s">
+      <c r="B14" s="408" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="408"/>
-      <c r="D14" s="409"/>
+      <c r="C14" s="409"/>
+      <c r="D14" s="410"/>
       <c r="N14" s="139"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="410" t="s">
+      <c r="B15" s="411" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="411"/>
-      <c r="D15" s="412"/>
+      <c r="C15" s="412"/>
+      <c r="D15" s="413"/>
       <c r="N15" s="139"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -28332,164 +27150,164 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
   </mergeCells>
+  <conditionalFormatting sqref="C72:G72">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C82:G82">
+    <cfRule type="cellIs" dxfId="34" priority="10" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92:G92">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102:G102">
+    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C112:G112">
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C122:G122">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
+      <formula>$C$70</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H72">
-    <cfRule type="cellIs" dxfId="84" priority="219" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="219" operator="greaterThan">
       <formula>$H$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="cellIs" dxfId="83" priority="202" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="202" operator="greaterThan">
       <formula>$H$81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H92">
-    <cfRule type="cellIs" dxfId="82" priority="192" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="192" operator="greaterThan">
       <formula>$H$91</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H112">
-    <cfRule type="cellIs" dxfId="81" priority="181" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="181" operator="greaterThan">
       <formula>$H$111</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H122">
-    <cfRule type="cellIs" dxfId="80" priority="171" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="171" operator="greaterThan">
       <formula>$H$121</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H102:L102">
-    <cfRule type="cellIs" dxfId="79" priority="187" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="187" operator="greaterThan">
       <formula>$C$101</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I72">
-    <cfRule type="cellIs" dxfId="78" priority="218" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="218" operator="greaterThan">
       <formula>$I$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82">
-    <cfRule type="cellIs" dxfId="77" priority="201" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="201" operator="greaterThan">
       <formula>$I$81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I92">
-    <cfRule type="cellIs" dxfId="76" priority="191" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="191" operator="greaterThan">
       <formula>$I$91</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="cellIs" dxfId="75" priority="180" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="180" operator="greaterThan">
       <formula>$I$111</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="cellIs" dxfId="74" priority="170" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="170" operator="greaterThan">
       <formula>$I$121</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J72">
-    <cfRule type="cellIs" dxfId="73" priority="217" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="217" operator="greaterThan">
       <formula>$J$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="cellIs" dxfId="72" priority="200" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="200" operator="greaterThan">
       <formula>$J$81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J92">
-    <cfRule type="cellIs" dxfId="71" priority="190" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="190" operator="greaterThan">
       <formula>$J$91</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J112">
-    <cfRule type="cellIs" dxfId="70" priority="179" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="179" operator="greaterThan">
       <formula>$J$111</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J122">
-    <cfRule type="cellIs" dxfId="69" priority="169" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="169" operator="greaterThan">
       <formula>$J$121</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72">
-    <cfRule type="cellIs" dxfId="68" priority="216" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="216" operator="greaterThan">
       <formula>$K$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K82">
-    <cfRule type="cellIs" dxfId="67" priority="199" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="199" operator="greaterThan">
       <formula>$K$81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K92">
-    <cfRule type="cellIs" dxfId="66" priority="189" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="189" operator="greaterThan">
       <formula>$K$91</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K112">
-    <cfRule type="cellIs" dxfId="65" priority="178" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="178" operator="greaterThan">
       <formula>$K$111</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K122">
-    <cfRule type="cellIs" dxfId="64" priority="168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="168" operator="greaterThan">
       <formula>$K$121</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L72">
-    <cfRule type="cellIs" dxfId="63" priority="215" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="215" operator="greaterThan">
       <formula>$L$70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L82">
-    <cfRule type="cellIs" dxfId="62" priority="198" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="198" operator="greaterThan">
       <formula>$L$81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L92">
-    <cfRule type="cellIs" dxfId="61" priority="188" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="188" operator="greaterThan">
       <formula>$L$91</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112">
-    <cfRule type="cellIs" dxfId="60" priority="177" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="177" operator="greaterThan">
       <formula>$L$111</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L122">
-    <cfRule type="cellIs" dxfId="59" priority="167" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThan">
       <formula>$L$121</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C72:G72">
-    <cfRule type="cellIs" dxfId="5" priority="12" operator="greaterThan">
-      <formula>$C$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C82:G82">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
-      <formula>$C$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92:G92">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="greaterThan">
-      <formula>$C$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102:G102">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
-      <formula>$C$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C112:G112">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
-      <formula>$C$70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C122:G122">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>$C$70</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -28569,101 +27387,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="211" id="{0B4D75C4-D25A-44EA-B63E-E03692154A69}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"h60"</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"h60"</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="210" id="{D9A4611E-EAFB-4D72-8EA7-BB20C2AA53D0}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"i60"</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>"i60"</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="209" id="{FC9241E0-399F-4612-9178-0FDDFFF0E42A}">
-            <x14:iconSet iconSet="3Symbols2" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$J$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>$J$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>J72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="208" id="{DD71F70E-9732-4C09-96AD-AC28A6D96762}">
-            <x14:iconSet iconSet="3Symbols2" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$K$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$K$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>K72</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="166" id="{C970D36A-412D-482A-B900-0C93FEFDE178}">
-            <x14:iconSet iconSet="3Symbols" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$L$70</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>$L$70</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L72</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="11" id="{536B711C-2A93-3745-B644-9671CF4BB432}">
             <x14:iconSet iconSet="3Symbols2" custom="1">
@@ -28778,6 +27501,101 @@
           </x14:cfRule>
           <xm:sqref>C122:G122</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="211" id="{0B4D75C4-D25A-44EA-B63E-E03692154A69}">
+            <x14:iconSet iconSet="3Symbols" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"h60"</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"h60"</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="210" id="{D9A4611E-EAFB-4D72-8EA7-BB20C2AA53D0}">
+            <x14:iconSet iconSet="3Symbols" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"i60"</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>"i60"</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="209" id="{FC9241E0-399F-4612-9178-0FDDFFF0E42A}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$J$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>$J$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="208" id="{DD71F70E-9732-4C09-96AD-AC28A6D96762}">
+            <x14:iconSet iconSet="3Symbols2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$K$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$K$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>K72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="166" id="{C970D36A-412D-482A-B900-0C93FEFDE178}">
+            <x14:iconSet iconSet="3Symbols" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$L$70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>$L$70</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L72</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -28857,62 +27675,62 @@
       <c r="G5" s="185" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="439" t="s">
+      <c r="I5" s="435" t="s">
         <v>423</v>
       </c>
-      <c r="J5" s="440"/>
-      <c r="K5" s="440"/>
-      <c r="L5" s="440"/>
-      <c r="M5" s="440"/>
-      <c r="N5" s="440"/>
-      <c r="O5" s="440"/>
-      <c r="P5" s="440"/>
-      <c r="Q5" s="440"/>
-      <c r="R5" s="440"/>
-      <c r="S5" s="440"/>
-      <c r="T5" s="440"/>
-      <c r="U5" s="440"/>
-      <c r="V5" s="440"/>
-      <c r="W5" s="441"/>
+      <c r="J5" s="436"/>
+      <c r="K5" s="436"/>
+      <c r="L5" s="436"/>
+      <c r="M5" s="436"/>
+      <c r="N5" s="436"/>
+      <c r="O5" s="436"/>
+      <c r="P5" s="436"/>
+      <c r="Q5" s="436"/>
+      <c r="R5" s="436"/>
+      <c r="S5" s="436"/>
+      <c r="T5" s="436"/>
+      <c r="U5" s="436"/>
+      <c r="V5" s="436"/>
+      <c r="W5" s="437"/>
       <c r="Y5" s="192"/>
       <c r="Z5" s="192"/>
       <c r="AA5" s="192"/>
       <c r="AB5" s="334"/>
     </row>
     <row r="6" spans="1:53" s="184" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="428" t="s">
+      <c r="B6" s="427" t="s">
         <v>228</v>
       </c>
-      <c r="C6" s="429"/>
-      <c r="D6" s="429"/>
-      <c r="E6" s="429"/>
-      <c r="F6" s="429"/>
-      <c r="G6" s="430"/>
-      <c r="I6" s="442" t="s">
+      <c r="C6" s="428"/>
+      <c r="D6" s="428"/>
+      <c r="E6" s="428"/>
+      <c r="F6" s="428"/>
+      <c r="G6" s="429"/>
+      <c r="I6" s="438" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="426" t="s">
+      <c r="J6" s="440" t="s">
         <v>409</v>
       </c>
-      <c r="K6" s="426" t="s">
+      <c r="K6" s="440" t="s">
         <v>408</v>
       </c>
-      <c r="L6" s="444" t="s">
+      <c r="L6" s="441" t="s">
         <v>215</v>
       </c>
-      <c r="M6" s="445"/>
-      <c r="N6" s="445"/>
-      <c r="O6" s="445"/>
-      <c r="P6" s="445"/>
-      <c r="Q6" s="446"/>
-      <c r="R6" s="431" t="s">
+      <c r="M6" s="442"/>
+      <c r="N6" s="442"/>
+      <c r="O6" s="442"/>
+      <c r="P6" s="442"/>
+      <c r="Q6" s="443"/>
+      <c r="R6" s="444" t="s">
         <v>216</v>
       </c>
-      <c r="S6" s="432"/>
-      <c r="T6" s="432"/>
-      <c r="U6" s="432"/>
-      <c r="V6" s="432"/>
-      <c r="W6" s="433"/>
+      <c r="S6" s="445"/>
+      <c r="T6" s="445"/>
+      <c r="U6" s="445"/>
+      <c r="V6" s="445"/>
+      <c r="W6" s="446"/>
       <c r="Y6" s="307"/>
       <c r="Z6" s="307"/>
       <c r="AA6" s="307"/>
@@ -28938,9 +27756,9 @@
         <f>SUM(C7:F7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="443"/>
-      <c r="J7" s="443"/>
-      <c r="K7" s="443"/>
+      <c r="I7" s="439"/>
+      <c r="J7" s="439"/>
+      <c r="K7" s="439"/>
       <c r="L7" s="186" t="s">
         <v>410</v>
       </c>
@@ -29144,14 +27962,14 @@
       <c r="AZ9" s="285"/>
     </row>
     <row r="10" spans="1:53" s="192" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="B10" s="434" t="s">
+      <c r="B10" s="430" t="s">
         <v>237</v>
       </c>
-      <c r="C10" s="434"/>
-      <c r="D10" s="434"/>
-      <c r="E10" s="434"/>
-      <c r="F10" s="434"/>
-      <c r="G10" s="434"/>
+      <c r="C10" s="430"/>
+      <c r="D10" s="430"/>
+      <c r="E10" s="430"/>
+      <c r="F10" s="430"/>
+      <c r="G10" s="430"/>
       <c r="I10" s="244" t="s">
         <v>231</v>
       </c>
@@ -29635,13 +28453,13 @@
       <c r="B16" s="193" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="435" t="s">
+      <c r="C16" s="431" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="436"/>
-      <c r="E16" s="436"/>
-      <c r="F16" s="436"/>
-      <c r="G16" s="437"/>
+      <c r="D16" s="432"/>
+      <c r="E16" s="432"/>
+      <c r="F16" s="432"/>
+      <c r="G16" s="433"/>
       <c r="I16" s="244" t="s">
         <v>404</v>
       </c>
@@ -29757,59 +28575,59 @@
     </row>
     <row r="18" spans="2:58" s="192" customFormat="1" ht="14" x14ac:dyDescent="0.15"/>
     <row r="19" spans="2:58" s="192" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I19" s="438" t="s">
+      <c r="I19" s="434" t="s">
         <v>424</v>
       </c>
-      <c r="J19" s="438"/>
-      <c r="K19" s="438"/>
-      <c r="L19" s="438"/>
-      <c r="M19" s="438"/>
-      <c r="N19" s="438"/>
-      <c r="O19" s="438"/>
-      <c r="P19" s="438"/>
-      <c r="Q19" s="438"/>
-      <c r="R19" s="438"/>
-      <c r="S19" s="438"/>
-      <c r="T19" s="438"/>
-      <c r="U19" s="438"/>
+      <c r="J19" s="434"/>
+      <c r="K19" s="434"/>
+      <c r="L19" s="434"/>
+      <c r="M19" s="434"/>
+      <c r="N19" s="434"/>
+      <c r="O19" s="434"/>
+      <c r="P19" s="434"/>
+      <c r="Q19" s="434"/>
+      <c r="R19" s="434"/>
+      <c r="S19" s="434"/>
+      <c r="T19" s="434"/>
+      <c r="U19" s="434"/>
       <c r="Z19" s="250"/>
       <c r="AA19" s="250"/>
       <c r="AB19" s="250"/>
       <c r="AC19" s="250"/>
     </row>
     <row r="20" spans="2:58" s="192" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I20" s="426" t="s">
+      <c r="I20" s="440" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="426" t="s">
+      <c r="J20" s="440" t="s">
         <v>213</v>
       </c>
-      <c r="K20" s="426" t="s">
+      <c r="K20" s="440" t="s">
         <v>214</v>
       </c>
-      <c r="L20" s="428" t="s">
+      <c r="L20" s="427" t="s">
         <v>215</v>
       </c>
-      <c r="M20" s="429"/>
-      <c r="N20" s="429"/>
-      <c r="O20" s="429"/>
-      <c r="P20" s="430"/>
-      <c r="Q20" s="431" t="s">
+      <c r="M20" s="428"/>
+      <c r="N20" s="428"/>
+      <c r="O20" s="428"/>
+      <c r="P20" s="429"/>
+      <c r="Q20" s="444" t="s">
         <v>216</v>
       </c>
-      <c r="R20" s="432"/>
-      <c r="S20" s="432"/>
-      <c r="T20" s="432"/>
-      <c r="U20" s="433"/>
+      <c r="R20" s="445"/>
+      <c r="S20" s="445"/>
+      <c r="T20" s="445"/>
+      <c r="U20" s="446"/>
       <c r="Z20" s="254"/>
       <c r="AA20" s="254"/>
       <c r="AB20" s="254"/>
       <c r="AC20" s="254"/>
     </row>
     <row r="21" spans="2:58" s="192" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I21" s="427"/>
-      <c r="J21" s="427"/>
-      <c r="K21" s="427"/>
+      <c r="I21" s="447"/>
+      <c r="J21" s="447"/>
+      <c r="K21" s="447"/>
       <c r="L21" s="186" t="s">
         <v>218</v>
       </c>
@@ -30831,6 +29649,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="Q20:U20"/>
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="C16:G16"/>
@@ -30841,11 +29664,6 @@
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:Q6"/>
     <mergeCell ref="R6:W6"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:P20"/>
-    <mergeCell ref="Q20:U20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31198,15 +30016,15 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="414" t="s">
+      <c r="A3" s="415" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="414"/>
-      <c r="C3" s="414"/>
-      <c r="D3" s="414"/>
-      <c r="E3" s="414"/>
-      <c r="F3" s="414"/>
-      <c r="G3" s="414"/>
+      <c r="B3" s="415"/>
+      <c r="C3" s="415"/>
+      <c r="D3" s="415"/>
+      <c r="E3" s="415"/>
+      <c r="F3" s="415"/>
+      <c r="G3" s="415"/>
       <c r="H3" s="82"/>
       <c r="I3" s="82"/>
       <c r="J3" s="82"/>
@@ -31222,13 +30040,13 @@
       <c r="B4" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="415" t="s">
+      <c r="C4" s="416" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="416"/>
-      <c r="E4" s="416"/>
-      <c r="F4" s="416"/>
-      <c r="G4" s="417"/>
+      <c r="D4" s="417"/>
+      <c r="E4" s="417"/>
+      <c r="F4" s="417"/>
+      <c r="G4" s="418"/>
       <c r="N4" s="136" t="s">
         <v>128</v>
       </c>
@@ -31238,11 +30056,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="111"/>
-      <c r="C5" s="418"/>
-      <c r="D5" s="413"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="413"/>
+      <c r="C5" s="419"/>
+      <c r="D5" s="414"/>
+      <c r="E5" s="414"/>
+      <c r="F5" s="414"/>
+      <c r="G5" s="414"/>
       <c r="N5" s="139"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -31250,11 +30068,11 @@
         <v>17</v>
       </c>
       <c r="B6" s="111"/>
-      <c r="C6" s="418"/>
-      <c r="D6" s="413"/>
-      <c r="E6" s="413"/>
-      <c r="F6" s="413"/>
-      <c r="G6" s="413"/>
+      <c r="C6" s="419"/>
+      <c r="D6" s="414"/>
+      <c r="E6" s="414"/>
+      <c r="F6" s="414"/>
+      <c r="G6" s="414"/>
       <c r="N6" s="139"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -31262,11 +30080,11 @@
         <v>18</v>
       </c>
       <c r="B7" s="111"/>
-      <c r="C7" s="418"/>
-      <c r="D7" s="413"/>
-      <c r="E7" s="413"/>
-      <c r="F7" s="413"/>
-      <c r="G7" s="413"/>
+      <c r="C7" s="419"/>
+      <c r="D7" s="414"/>
+      <c r="E7" s="414"/>
+      <c r="F7" s="414"/>
+      <c r="G7" s="414"/>
       <c r="N7" s="139"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -31274,11 +30092,11 @@
         <v>39</v>
       </c>
       <c r="B8" s="88"/>
-      <c r="C8" s="413"/>
-      <c r="D8" s="413"/>
-      <c r="E8" s="413"/>
-      <c r="F8" s="413"/>
-      <c r="G8" s="413"/>
+      <c r="C8" s="414"/>
+      <c r="D8" s="414"/>
+      <c r="E8" s="414"/>
+      <c r="F8" s="414"/>
+      <c r="G8" s="414"/>
       <c r="N8" s="139"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -31286,11 +30104,11 @@
         <v>162</v>
       </c>
       <c r="B9" s="88"/>
-      <c r="C9" s="419"/>
-      <c r="D9" s="419"/>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="419"/>
+      <c r="C9" s="420"/>
+      <c r="D9" s="420"/>
+      <c r="E9" s="420"/>
+      <c r="F9" s="420"/>
+      <c r="G9" s="420"/>
       <c r="N9" s="139"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -31298,11 +30116,11 @@
         <v>40</v>
       </c>
       <c r="B10" s="112"/>
-      <c r="C10" s="447"/>
-      <c r="D10" s="447"/>
-      <c r="E10" s="447"/>
-      <c r="F10" s="447"/>
-      <c r="G10" s="447"/>
+      <c r="C10" s="449"/>
+      <c r="D10" s="449"/>
+      <c r="E10" s="449"/>
+      <c r="F10" s="449"/>
+      <c r="G10" s="449"/>
       <c r="N10" s="139"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -31315,37 +30133,37 @@
       <c r="A12" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="420" t="s">
+      <c r="B12" s="421" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="421"/>
-      <c r="D12" s="422"/>
+      <c r="C12" s="422"/>
+      <c r="D12" s="423"/>
       <c r="N12" s="138" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="423" t="s">
+      <c r="B13" s="424" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="424"/>
-      <c r="D13" s="425"/>
+      <c r="C13" s="425"/>
+      <c r="D13" s="426"/>
       <c r="N13" s="139"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="407" t="s">
+      <c r="B14" s="408" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="408"/>
-      <c r="D14" s="409"/>
+      <c r="C14" s="409"/>
+      <c r="D14" s="410"/>
       <c r="N14" s="139"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="410" t="s">
+      <c r="B15" s="411" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="411"/>
-      <c r="D15" s="412"/>
+      <c r="C15" s="412"/>
+      <c r="D15" s="413"/>
       <c r="N15" s="139"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -32565,12 +31383,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
@@ -32578,6 +31390,12 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N4" r:id="rId1" location="step-1-assign-parties-person-playing-and-strategies" xr:uid="{726B234F-7B54-4D33-A192-8F1604C6B04C}"/>
@@ -32633,26 +31451,26 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="449" t="s">
+      <c r="D3" s="450" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="449"/>
-      <c r="F3" s="449" t="s">
+      <c r="E3" s="450"/>
+      <c r="F3" s="450" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="449"/>
-      <c r="H3" s="449"/>
-      <c r="I3" s="449" t="s">
+      <c r="G3" s="450"/>
+      <c r="H3" s="450"/>
+      <c r="I3" s="450" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="449"/>
-      <c r="K3" s="449"/>
+      <c r="J3" s="450"/>
+      <c r="K3" s="450"/>
       <c r="L3" s="131"/>
-      <c r="M3" s="449" t="s">
+      <c r="M3" s="450" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="449"/>
-      <c r="O3" s="449"/>
+      <c r="N3" s="450"/>
+      <c r="O3" s="450"/>
     </row>
     <row r="4" spans="1:16" s="45" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
@@ -33950,16 +32768,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>$B$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>$B$8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>$B$9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>$B$10</formula>
     </cfRule>
   </conditionalFormatting>

--- a/LakeMeadWaterBankDivideInflow.xlsx
+++ b/LakeMeadWaterBankDivideInflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anabelle/Documents/LakeMeadDivideInflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA9146B-B985-1A49-903B-4C59A3160FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC933262-534A-454F-82B8-5AEA39837178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" firstSheet="1" activeTab="3" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
+    <workbookView xWindow="-17120" yWindow="-23500" windowWidth="38400" windowHeight="23500" activeTab="2" xr2:uid="{5373AB19-D84C-490D-97DC-C516D358024A}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe-Directions" sheetId="62" r:id="rId1"/>
@@ -5051,7 +5051,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EBF23E2E-2F5E-FB42-AB63-DB931375975D}" type="CELLRANGE">
+                    <a:fld id="{6E70598F-89E7-164C-A98B-602179E504E6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5084,7 +5084,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8A0C4FBB-5355-F74D-8D2D-2DA38038DF79}" type="CELLRANGE">
+                    <a:fld id="{04C0E1BD-9565-0745-9891-7EA626C83622}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5118,7 +5118,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{66CE1E64-6E6C-A741-B9FF-B1A3E14E1789}" type="CELLRANGE">
+                    <a:fld id="{6BCD8B03-4CDE-4640-80A8-78EBF4B1CCCA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5152,7 +5152,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EF0F5A83-36EC-DD46-B776-7BA8596A5862}" type="CELLRANGE">
+                    <a:fld id="{8C82F45A-9BA0-4D48-871A-108632177E66}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5186,7 +5186,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC116C19-4A6D-AA4C-B54B-A647C8D03CA9}" type="CELLRANGE">
+                    <a:fld id="{444645C7-9EC2-EA44-BFCB-6E115325B348}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5342,7 +5342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F8CB4F4-6ECE-BD4A-A6CF-972CCFFC0562}" type="CELLRANGE">
+                    <a:fld id="{A9410BD3-2495-AD4A-803F-D17C5138F1A2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5375,7 +5375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{31CA6072-10E9-3C46-AD06-97316F64A592}" type="CELLRANGE">
+                    <a:fld id="{8BA5CA0D-D6ED-6743-92DF-19B2561FEA9D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5409,7 +5409,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A2E39BFE-8B1A-4745-B200-94F346C83CED}" type="CELLRANGE">
+                    <a:fld id="{DCEB9048-9DA7-444A-8F20-20CD25AD0F7D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5443,7 +5443,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2499BB8C-F587-4146-BB34-6DFF93EFC078}" type="CELLRANGE">
+                    <a:fld id="{10E33572-DEE8-8945-B355-024673BE1393}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5477,7 +5477,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0CAC97C-DF1B-C04B-B61D-C49F5543031C}" type="CELLRANGE">
+                    <a:fld id="{460E3AA7-CDE6-1949-A9C4-AB7A18DB7B5F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5610,7 +5610,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{49AE8E98-D96E-C74A-A99E-99AFC189000D}" type="CELLRANGE">
+                    <a:fld id="{C5F3AE2C-49F0-EC42-8C4F-8C51D2340F9A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5643,7 +5643,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E54DE757-4BBD-8146-BDD1-459DE9235F07}" type="CELLRANGE">
+                    <a:fld id="{8E0A9E27-DED6-1743-81A9-5D545C9838BE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5677,7 +5677,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A9916F2-E79C-3C45-B378-EFB0C341D866}" type="CELLRANGE">
+                    <a:fld id="{E11A914B-EF5A-E844-BC8C-BC7783E1BA49}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5711,7 +5711,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EF8C5855-4A3D-AD48-BCE2-1004A84A0B77}" type="CELLRANGE">
+                    <a:fld id="{A38663B7-0263-8242-85D8-876E8791783D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5745,7 +5745,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A6ACAE26-E4F5-BB48-874C-D4A022864063}" type="CELLRANGE">
+                    <a:fld id="{0A18C7F7-81FC-764E-BA9E-2BF64DC8E68A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5878,7 +5878,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AA38807-3F44-174F-AE74-16901B16D683}" type="CELLRANGE">
+                    <a:fld id="{B5FA6252-4AD9-6149-A7A1-B32EE5F2ABC9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5911,7 +5911,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA692FE6-6F5B-F34C-B0B7-25516FD9289C}" type="CELLRANGE">
+                    <a:fld id="{2975D5B6-52A4-364D-B3F7-8F63084316D9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5945,7 +5945,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D0F4FE8-8FB3-DE4D-A163-B8FBEEA93F87}" type="CELLRANGE">
+                    <a:fld id="{04BC8B47-0008-5340-B8EE-6012A1D755F2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5979,7 +5979,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F2AB8AB9-16A2-8147-B77F-158196B08B7C}" type="CELLRANGE">
+                    <a:fld id="{E04CDF24-3565-F84E-A996-0758D743F20A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6013,7 +6013,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A83C57D0-9F1A-F34F-87F2-0CA72509BA10}" type="CELLRANGE">
+                    <a:fld id="{31DB7CF8-06DA-8B41-82DB-C27CDC147366}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6169,7 +6169,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81E1F7EE-DB72-B744-BFEE-FCDC577E285A}" type="CELLRANGE">
+                    <a:fld id="{38164397-6274-ED4E-AAA9-83DD80388A06}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6202,7 +6202,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5113DD99-3FF1-E547-AA39-EE50B5AAF7E6}" type="CELLRANGE">
+                    <a:fld id="{CA68695B-D25A-2045-992E-7004040D4D7A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6236,7 +6236,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F99E226C-D08B-D447-8FF9-F10EC8FE6F2E}" type="CELLRANGE">
+                    <a:fld id="{88649BC3-CE53-A247-91B7-B844B027D8C0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6270,7 +6270,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3EA03092-5907-A743-A0DA-EBBEB9478A2C}" type="CELLRANGE">
+                    <a:fld id="{90894306-BA8C-CF47-B1C7-749C6FC2509E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6304,7 +6304,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C0310E57-564E-CF44-B4A8-C74C65553B22}" type="CELLRANGE">
+                    <a:fld id="{0DCB0EEB-AAF1-E049-89D0-353C0683E9E9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6463,7 +6463,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A65EA91E-A9EB-EC42-9E43-419836E2AF26}" type="CELLRANGE">
+                    <a:fld id="{17254A7A-D261-BE4D-A36E-CC8666B7EBA6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6496,7 +6496,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5451E50-1C5B-2C44-9A34-5533F3AECB67}" type="CELLRANGE">
+                    <a:fld id="{EF7383B1-2C21-1F43-B047-07AEDD9E5746}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6530,7 +6530,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9DD5FF91-74D7-3843-BCEB-9B2248D873DE}" type="CELLRANGE">
+                    <a:fld id="{9E6195CD-E64F-954A-BF89-0F79830A5B8A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6564,7 +6564,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{657CFC1C-66DF-674F-943A-7C46AD540C8A}" type="CELLRANGE">
+                    <a:fld id="{96FF326A-4BAC-B840-9212-E3E096DE4E9B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6598,7 +6598,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51EF811A-1335-FA4C-AB3A-DBD27D3018B1}" type="CELLRANGE">
+                    <a:fld id="{4FA7BEA0-D0C2-A147-A37F-934F4D4B2B04}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18053,7 +18053,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8678333" cy="6286500"/>
+    <xdr:ext cx="8669421" cy="6283158"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
